--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46228.54166666666</v>
+        <v>46228.52083333334</v>
       </c>
     </row>
     <row r="46">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.39</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
-        <v>5.3</v>
+        <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>6.06</v>
+        <v>2.32</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8787,27 +8787,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46228.5625</v>
+        <v>46228.54166666666</v>
       </c>
     </row>
     <row r="54">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46228.60416666666</v>
+        <v>46228.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -9105,27 +9105,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46228.61458333334</v>
+        <v>46228.5625</v>
       </c>
     </row>
     <row r="56">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46228.625</v>
+        <v>46228.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -9423,27 +9423,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9515,10 +9515,10 @@
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46228.625</v>
+        <v>46228.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -9582,27 +9582,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46228.625</v>
+        <v>46228.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.61458333334</v>
       </c>
     </row>
     <row r="61">
@@ -10059,27 +10059,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="62">
@@ -10218,27 +10218,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="63">
@@ -10377,27 +10377,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="65">
@@ -10695,27 +10695,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46228.65625</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="66">
@@ -10854,27 +10854,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="67">
@@ -11013,27 +11013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11056,17 +11056,17 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -11172,27 +11172,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="69">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="70">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>46228.70833333334</v>
+        <v>46228.65625</v>
       </c>
     </row>
     <row r="71">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>46228.70833333334</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="72">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>46228.75</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="73">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="74">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.70833333334</v>
       </c>
     </row>
     <row r="76">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.70833333334</v>
       </c>
     </row>
     <row r="77">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.75</v>
       </c>
     </row>
     <row r="78">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.76041666666</v>
       </c>
     </row>
     <row r="79">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>46228.79166666666</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="80">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>46228.79166666666</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="81">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>46228.8125</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="82">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="83">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="84">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.79166666666</v>
       </c>
     </row>
     <row r="85">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.79166666666</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.8125</v>
       </c>
     </row>
     <row r="87">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="89">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="91">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="92">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="93">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46228.86458333334</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="98">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="AU98" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="99">
@@ -16101,27 +16101,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16251,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="AU99" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="100">
@@ -16260,27 +16260,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="101">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.86458333334</v>
       </c>
     </row>
     <row r="102">
@@ -16583,22 +16583,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,22 +18173,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,22 +18332,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,22 +18650,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18954,7 +18954,7 @@
         <v>0</v>
       </c>
       <c r="AU116" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.875</v>
       </c>
     </row>
     <row r="117">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="121">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46228.9375</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="123">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20067,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="AU123" s="3" t="n">
-        <v>46228.95833333334</v>
+        <v>46228.9375</v>
       </c>
     </row>
     <row r="124">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20385,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="AU125" s="3" t="n">
-        <v>46228.97916666666</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="126">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20862,6 +20862,165 @@
         <v>0</v>
       </c>
       <c r="AU128" s="3" t="n">
+        <v>46228.97916666666</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" s="3" t="n">
         <v>46228.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="P50" t="n">
-        <v>2.32</v>
+        <v>3.61</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P67" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O68" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,22 +17537,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20886,12 +20886,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="O54" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>3.61</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P68" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O80" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P80" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,22 +17537,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,22 +17696,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,22 +18650,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20886,12 +20886,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O68" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16144,17 +16144,17 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16583,22 +16583,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,22 +17537,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,22 +17696,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -20886,12 +20886,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>2.27</v>
       </c>
       <c r="O28" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O41" t="n">
         <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15508,17 +15508,17 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,22 +17855,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,22 +18491,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -20886,12 +20886,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O43" t="n">
         <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.39</v>
+        <v>3.31</v>
       </c>
       <c r="O46" t="n">
-        <v>5.3</v>
+        <v>3.26</v>
       </c>
       <c r="P46" t="n">
-        <v>6.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,22 +17537,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,22 +17696,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,22 +17855,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,22 +18173,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18650,22 +18650,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU129"/>
+  <dimension ref="A1:AU125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6084,27 +6084,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46228.45833333334</v>
+        <v>46228.5</v>
       </c>
     </row>
     <row r="37">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46228.5</v>
+        <v>46228.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46228.52083333334</v>
+        <v>46228.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.31</v>
+        <v>1.39</v>
       </c>
       <c r="O46" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>6.06</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>6.06</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8946,27 +8946,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46228.54166666666</v>
+        <v>46228.5625</v>
       </c>
     </row>
     <row r="55">
@@ -9105,27 +9105,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46228.5625</v>
+        <v>46228.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46228.58333333334</v>
+        <v>46228.60416666666</v>
       </c>
     </row>
     <row r="59">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9833,10 +9833,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46228.60416666666</v>
+        <v>46228.61458333334</v>
       </c>
     </row>
     <row r="60">
@@ -9900,27 +9900,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46228.61458333334</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="61">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46228.625</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="64">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10854,27 +10854,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O67" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11331,27 +11331,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="O69" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="P69" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.65625</v>
       </c>
     </row>
     <row r="70">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>46228.65625</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="71">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.70833333334</v>
       </c>
     </row>
     <row r="75">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>46228.70833333334</v>
+        <v>46228.75</v>
       </c>
     </row>
     <row r="77">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12753,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>46228.75</v>
+        <v>46228.76041666666</v>
       </c>
     </row>
     <row r="78">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="79">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O79" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P79" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="O80" t="n">
-        <v>4.29</v>
+        <v>3.34</v>
       </c>
       <c r="P80" t="n">
-        <v>6.63</v>
+        <v>3.98</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.79166666666</v>
       </c>
     </row>
     <row r="84">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46228.79166666666</v>
+        <v>46228.8125</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46228.8125</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="87">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="93">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.86458333334</v>
       </c>
     </row>
     <row r="101">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46228.86458333334</v>
+        <v>46228.875</v>
       </c>
     </row>
     <row r="102">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,22 +17696,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,22 +18173,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18477,7 +18477,7 @@
         <v>0</v>
       </c>
       <c r="AU113" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="114">
@@ -18486,27 +18486,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18636,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="AU114" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="115">
@@ -18645,12 +18645,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18795,7 +18795,7 @@
         <v>0</v>
       </c>
       <c r="AU115" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="116">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18954,7 +18954,7 @@
         <v>0</v>
       </c>
       <c r="AU116" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="117">
@@ -18963,12 +18963,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="AU117" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="118">
@@ -19122,12 +19122,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="AU118" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="119">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19431,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="AU119" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.9375</v>
       </c>
     </row>
     <row r="120">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="121">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19749,7 +19749,7 @@
         <v>0</v>
       </c>
       <c r="AU121" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="122">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.97916666666</v>
       </c>
     </row>
     <row r="123">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -20067,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="AU123" s="3" t="n">
-        <v>46228.9375</v>
+        <v>46228.97916666666</v>
       </c>
     </row>
     <row r="124">
@@ -20076,12 +20076,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20226,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="AU124" s="3" t="n">
-        <v>46228.95833333334</v>
+        <v>46228.97916666666</v>
       </c>
     </row>
     <row r="125">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20385,642 +20385,6 @@
         <v>0</v>
       </c>
       <c r="AU125" s="3" t="n">
-        <v>46228.95833333334</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU126" s="3" t="n">
-        <v>46228.97916666666</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP127" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU127" s="3" t="n">
-        <v>46228.97916666666</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU128" s="3" t="n">
-        <v>46228.97916666666</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU129" s="3" t="n">
         <v>46228.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.27</v>
+        <v>4.84</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O42" t="n">
         <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="O46" t="n">
-        <v>5.3</v>
+        <v>3.84</v>
       </c>
       <c r="P46" t="n">
-        <v>6.06</v>
+        <v>3.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.31</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2.04</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.72</v>
+        <v>3.31</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="P50" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O80" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P80" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O88" t="n">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="P88" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="O89" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="P89" t="n">
-        <v>3.92</v>
+        <v>4.9</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="O91" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="P91" t="n">
-        <v>4.9</v>
+        <v>3.92</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,22 +17537,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,22 +18173,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -19526,10 +19526,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20162,10 +20162,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU125"/>
+  <dimension ref="A1:AU126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="O40" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,49 +7721,49 @@
         </is>
       </c>
       <c r="N46" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>1.84</v>
       </c>
-      <c r="O46" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="O47" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="P47" t="n">
-        <v>2.32</v>
+        <v>3.61</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.86</v>
+        <v>2.72</v>
       </c>
       <c r="O49" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>2.32</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="O53" t="n">
-        <v>5.3</v>
+        <v>3.84</v>
       </c>
       <c r="P53" t="n">
-        <v>6.06</v>
+        <v>3.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O90" t="n">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P90" t="n">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18477,7 +18477,7 @@
         <v>0</v>
       </c>
       <c r="AU113" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.875</v>
       </c>
     </row>
     <row r="114">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18963,12 +18963,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="AU117" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="118">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="AU119" s="3" t="n">
-        <v>46228.9375</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="120">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -19526,10 +19526,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46228.95833333334</v>
+        <v>46228.9375</v>
       </c>
     </row>
     <row r="121">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46228.97916666666</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="123">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20162,10 +20162,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20385,6 +20385,165 @@
         <v>0</v>
       </c>
       <c r="AU125" s="3" t="n">
+        <v>46228.97916666666</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O126" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" s="3" t="n">
         <v>46228.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="O53" t="n">
-        <v>3.84</v>
+        <v>5.3</v>
       </c>
       <c r="P53" t="n">
-        <v>3.8</v>
+        <v>6.06</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,14 +10901,14 @@
         </is>
       </c>
       <c r="N66" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P66" t="n">
         <v>2.45</v>
       </c>
-      <c r="O66" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P66" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P67" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O68" t="n">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="P68" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,16 +11258,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="O86" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P86" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O87" t="n">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P87" t="n">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O90" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="P90" t="n">
-        <v>3.92</v>
+        <v>2.75</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,22 +18173,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,10 +20003,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20480,10 +20480,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
         <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.97</v>
+        <v>3.86</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O47" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="P47" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="O50" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="P50" t="n">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="O52" t="n">
-        <v>3.72</v>
+        <v>5.3</v>
       </c>
       <c r="P52" t="n">
-        <v>2.32</v>
+        <v>6.06</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.39</v>
+        <v>3.31</v>
       </c>
       <c r="O53" t="n">
-        <v>5.3</v>
+        <v>3.26</v>
       </c>
       <c r="P53" t="n">
-        <v>6.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="O66" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P66" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,14 +11219,14 @@
         </is>
       </c>
       <c r="N68" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P68" t="n">
         <v>2.45</v>
       </c>
-      <c r="O68" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O88" t="n">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="P88" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="O90" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="P90" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16424,22 +16424,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,10 +20003,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20321,10 +20321,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>2.27</v>
       </c>
       <c r="O28" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="O50" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="P50" t="n">
-        <v>3.61</v>
+        <v>6.06</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="O51" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="P51" t="n">
-        <v>2.32</v>
+        <v>5.95</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8561,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.31</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O67" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11105,10 +11105,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P68" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13967,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="O86" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="P86" t="n">
-        <v>4.9</v>
+        <v>3.92</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O88" t="n">
-        <v>3.35</v>
+        <v>4.81</v>
       </c>
       <c r="P88" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,16 +14438,16 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O90" t="n">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="P90" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15239,10 +15239,10 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15557,10 +15557,10 @@
         <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15826,17 +15826,17 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="O99" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="P99" t="n">
-        <v>4.28</v>
+        <v>3.11</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,22 +16424,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,22 +17855,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -19532,10 +19532,10 @@
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,10 +20003,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20168,10 +20168,10 @@
         <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2.06</v>
+        <v>1.21</v>
       </c>
       <c r="O125" t="n">
-        <v>3.4</v>
+        <v>7.95</v>
       </c>
       <c r="P125" t="n">
-        <v>3.1</v>
+        <v>12.7</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20321,16 +20321,16 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20486,10 +20486,10 @@
         <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.69</v>
+        <v>3.86</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O43" t="n">
         <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.31</v>
+        <v>1.84</v>
       </c>
       <c r="O46" t="n">
-        <v>3.26</v>
+        <v>3.84</v>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="O49" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P49" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="O50" t="n">
-        <v>5.3</v>
+        <v>3.78</v>
       </c>
       <c r="P50" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="O53" t="n">
-        <v>3.72</v>
+        <v>5.3</v>
       </c>
       <c r="P53" t="n">
-        <v>2.32</v>
+        <v>6.06</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8879,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O66" t="n">
-        <v>3.32</v>
+        <v>3.82</v>
       </c>
       <c r="P66" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,16 +10940,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O68" t="n">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="P68" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,16 +11258,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O86" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="P86" t="n">
-        <v>3.92</v>
+        <v>2.75</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="O87" t="n">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="P87" t="n">
-        <v>4.9</v>
+        <v>2.71</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O88" t="n">
-        <v>4.81</v>
+        <v>3.86</v>
       </c>
       <c r="P88" t="n">
-        <v>4.28</v>
+        <v>3.92</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14444,10 +14444,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="O89" t="n">
-        <v>3.06</v>
+        <v>4.81</v>
       </c>
       <c r="P89" t="n">
-        <v>2.71</v>
+        <v>4.28</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14603,10 +14603,10 @@
         <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="O92" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="P92" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15190,17 +15190,17 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15239,10 +15239,10 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="O94" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="P94" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.95</v>
+        <v>2.29</v>
       </c>
       <c r="O95" t="n">
-        <v>4.53</v>
+        <v>3.68</v>
       </c>
       <c r="P95" t="n">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,16 +15551,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15667,17 +15667,17 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15716,10 +15716,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="O98" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="P98" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="O99" t="n">
-        <v>3.68</v>
+        <v>4.18</v>
       </c>
       <c r="P99" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,16 +16187,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -16583,22 +16583,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,22 +16901,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,22 +17855,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18332,22 +18332,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>3.41</v>
+        <v>1.59</v>
       </c>
       <c r="O114" t="n">
-        <v>3.93</v>
+        <v>4.47</v>
       </c>
       <c r="P114" t="n">
-        <v>2.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="O123" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P123" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,16 +20003,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,55 +20123,55 @@
         </is>
       </c>
       <c r="N124" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O124" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P124" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
         <v>1.71</v>
       </c>
-      <c r="O124" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P124" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD124" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O125" t="n">
-        <v>7.95</v>
+        <v>4.65</v>
       </c>
       <c r="P125" t="n">
-        <v>12.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20327,10 +20327,10 @@
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="O126" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="P126" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20480,16 +20480,16 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="P12" t="n">
-        <v>2.93</v>
+        <v>2.07</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>4.84</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>3.28</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O41" t="n">
         <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
         <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.97</v>
+        <v>3.86</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.31</v>
+        <v>1.39</v>
       </c>
       <c r="O45" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>6.06</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.56</v>
+        <v>3.31</v>
       </c>
       <c r="O50" t="n">
-        <v>3.78</v>
+        <v>3.26</v>
       </c>
       <c r="P50" t="n">
-        <v>5.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O52" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="P52" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P64" t="n">
-        <v>6.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P67" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,14 +11219,14 @@
         </is>
       </c>
       <c r="N68" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P68" t="n">
         <v>2.45</v>
       </c>
-      <c r="O68" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O80" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P80" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="O86" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="P86" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O88" t="n">
-        <v>3.86</v>
+        <v>4.81</v>
       </c>
       <c r="P88" t="n">
-        <v>3.92</v>
+        <v>4.28</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14444,10 +14444,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O89" t="n">
-        <v>4.81</v>
+        <v>3.86</v>
       </c>
       <c r="P89" t="n">
-        <v>4.28</v>
+        <v>3.92</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14603,10 +14603,10 @@
         <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="O92" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P92" t="n">
-        <v>3.88</v>
+        <v>4.28</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15190,17 +15190,17 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="O94" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="P94" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="O95" t="n">
-        <v>3.68</v>
+        <v>4.18</v>
       </c>
       <c r="P95" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,16 +15551,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="O96" t="n">
-        <v>4.53</v>
+        <v>4.04</v>
       </c>
       <c r="P96" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,16 +15710,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15826,17 +15826,17 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="O98" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="P98" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O99" t="n">
-        <v>4.18</v>
+        <v>4.53</v>
       </c>
       <c r="P99" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16193,10 +16193,10 @@
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD99" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,22 +18332,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.59</v>
+        <v>3.41</v>
       </c>
       <c r="O114" t="n">
-        <v>4.47</v>
+        <v>3.93</v>
       </c>
       <c r="P114" t="n">
-        <v>5.56</v>
+        <v>2.07</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="O116" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="P116" t="n">
-        <v>4.16</v>
+        <v>5.56</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="O117" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P117" t="n">
-        <v>2.07</v>
+        <v>4.16</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="O123" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="P123" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,16 +20003,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O124" t="n">
-        <v>7.95</v>
+        <v>4.65</v>
       </c>
       <c r="P124" t="n">
-        <v>12.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20168,10 +20168,10 @@
         <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1.71</v>
+        <v>2.36</v>
       </c>
       <c r="O125" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="P125" t="n">
-        <v>4.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2.06</v>
+        <v>1.21</v>
       </c>
       <c r="O126" t="n">
-        <v>3.4</v>
+        <v>7.95</v>
       </c>
       <c r="P126" t="n">
-        <v>3.1</v>
+        <v>12.7</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20480,16 +20480,16 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P41" t="n">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="O45" t="n">
-        <v>5.3</v>
+        <v>3.78</v>
       </c>
       <c r="P45" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2.32</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="O51" t="n">
-        <v>3.78</v>
+        <v>5.3</v>
       </c>
       <c r="P51" t="n">
-        <v>5.95</v>
+        <v>6.06</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="O65" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P65" t="n">
-        <v>6.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O66" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P66" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10946,10 +10946,10 @@
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P68" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="O80" t="n">
-        <v>4.29</v>
+        <v>3.34</v>
       </c>
       <c r="P80" t="n">
-        <v>6.63</v>
+        <v>3.98</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14285,10 +14285,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O88" t="n">
-        <v>4.81</v>
+        <v>3.86</v>
       </c>
       <c r="P88" t="n">
-        <v>4.28</v>
+        <v>3.92</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14444,10 +14444,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O89" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="P89" t="n">
-        <v>3.92</v>
+        <v>2.75</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="O90" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P90" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="O91" t="n">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="P91" t="n">
-        <v>4.9</v>
+        <v>2.71</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.96</v>
+        <v>2.95</v>
       </c>
       <c r="O92" t="n">
-        <v>3.36</v>
+        <v>4.53</v>
       </c>
       <c r="P92" t="n">
-        <v>4.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15080,10 +15080,10 @@
         <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="O94" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P94" t="n">
-        <v>3.88</v>
+        <v>4.28</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="O95" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="P95" t="n">
-        <v>2.15</v>
+        <v>3.88</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,16 +15551,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
-        <v>4.04</v>
+        <v>4.18</v>
       </c>
       <c r="P96" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,16 +15710,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15826,17 +15826,17 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,17 +15985,17 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>1.98</v>
       </c>
       <c r="O99" t="n">
-        <v>4.53</v>
+        <v>3.96</v>
       </c>
       <c r="P99" t="n">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,16 +16187,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,22 +17378,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="O114" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P114" t="n">
-        <v>2.07</v>
+        <v>4.16</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="O117" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="P117" t="n">
-        <v>4.16</v>
+        <v>5.56</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>2.86</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="O41" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P42" t="n">
-        <v>3.86</v>
+        <v>2.69</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="O45" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="P45" t="n">
-        <v>5.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.72</v>
+        <v>1.84</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P46" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.31</v>
+        <v>1.86</v>
       </c>
       <c r="O47" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>3.61</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="O51" t="n">
-        <v>5.3</v>
+        <v>3.78</v>
       </c>
       <c r="P51" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14126,10 +14126,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O87" t="n">
-        <v>4.81</v>
+        <v>3.35</v>
       </c>
       <c r="P87" t="n">
-        <v>4.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,16 +14279,16 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="O89" t="n">
-        <v>3.35</v>
+        <v>3.86</v>
       </c>
       <c r="P89" t="n">
-        <v>2.75</v>
+        <v>3.92</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15080,10 +15080,10 @@
         <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="O93" t="n">
-        <v>3.68</v>
+        <v>3.96</v>
       </c>
       <c r="P93" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15985,17 +15985,17 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="O99" t="n">
-        <v>3.96</v>
+        <v>3.68</v>
       </c>
       <c r="P99" t="n">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,22 +16583,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.85</v>
+        <v>3.41</v>
       </c>
       <c r="O114" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="P114" t="n">
-        <v>4.16</v>
+        <v>2.07</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="O115" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P115" t="n">
-        <v>2.07</v>
+        <v>4.16</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.06</v>
+        <v>1.21</v>
       </c>
       <c r="O123" t="n">
-        <v>3.4</v>
+        <v>7.95</v>
       </c>
       <c r="P123" t="n">
-        <v>3.1</v>
+        <v>12.7</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20003,16 +20003,16 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="O124" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="P124" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20162,16 +20162,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O126" t="n">
-        <v>7.95</v>
+        <v>4.65</v>
       </c>
       <c r="P126" t="n">
-        <v>12.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20486,10 +20486,10 @@
         <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD126" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="O10" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>3.51</v>
+        <v>2.86</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.42</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2.07</v>
+        <v>2.93</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="O13" t="n">
-        <v>3.16</v>
+        <v>3.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.86</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.84</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>4.84</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="P28" t="n">
-        <v>3.28</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O43" t="n">
         <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.72</v>
+        <v>3.31</v>
       </c>
       <c r="O45" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="P45" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="O47" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="P47" t="n">
-        <v>3.61</v>
+        <v>5.95</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="O50" t="n">
-        <v>5.3</v>
+        <v>3.84</v>
       </c>
       <c r="P50" t="n">
-        <v>6.06</v>
+        <v>3.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="O51" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="P51" t="n">
-        <v>5.95</v>
+        <v>3.61</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P64" t="n">
-        <v>6.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="O66" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P66" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
-        <v>3.32</v>
+        <v>3.82</v>
       </c>
       <c r="P67" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,16 +11099,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O68" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O81" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P81" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.71</v>
+        <v>2.41</v>
       </c>
       <c r="O89" t="n">
-        <v>3.86</v>
+        <v>3.06</v>
       </c>
       <c r="P89" t="n">
-        <v>3.92</v>
+        <v>2.71</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O91" t="n">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P91" t="n">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="O93" t="n">
-        <v>3.96</v>
+        <v>4.18</v>
       </c>
       <c r="P93" t="n">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,16 +15233,16 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="O94" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P94" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="O95" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P95" t="n">
-        <v>3.88</v>
+        <v>4.28</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15667,17 +15667,17 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15716,10 +15716,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="O97" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="P97" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16424,22 +16424,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,22 +16583,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="O114" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="P114" t="n">
-        <v>2.07</v>
+        <v>4.16</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="O115" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="P115" t="n">
-        <v>4.16</v>
+        <v>5.56</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19844,10 +19844,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O123" t="n">
-        <v>7.95</v>
+        <v>4.65</v>
       </c>
       <c r="P123" t="n">
-        <v>12.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20009,10 +20009,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="O124" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P124" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20162,16 +20162,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2.36</v>
+        <v>1.21</v>
       </c>
       <c r="O125" t="n">
-        <v>4.3</v>
+        <v>7.95</v>
       </c>
       <c r="P125" t="n">
-        <v>2.67</v>
+        <v>12.7</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20327,10 +20327,10 @@
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20409,12 +20409,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20441,13 +20441,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="O126" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="P126" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -20480,16 +20480,16 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU126"/>
+  <dimension ref="A1:AU128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.42</v>
+        <v>2.19</v>
       </c>
       <c r="O11" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.93</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
         <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.97</v>
+        <v>3.86</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.31</v>
+        <v>1.39</v>
       </c>
       <c r="O45" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>6.06</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="O47" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="P47" t="n">
-        <v>5.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P48" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="O52" t="n">
-        <v>5.3</v>
+        <v>3.78</v>
       </c>
       <c r="P52" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="O61" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="P61" t="n">
-        <v>5.67</v>
+        <v>5.33</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="64">
@@ -10536,27 +10536,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,49 +10583,49 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O64" t="n">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="P64" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="65">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46228.63541666666</v>
+        <v>46228.625</v>
       </c>
     </row>
     <row r="66">
@@ -10854,27 +10854,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.45</v>
+        <v>1.46</v>
       </c>
       <c r="O66" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P66" t="n">
-        <v>2.5</v>
+        <v>6.34</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="67">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.51</v>
+        <v>5.1</v>
       </c>
       <c r="O67" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P67" t="n">
-        <v>2.43</v>
+        <v>1.63</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,16 +11099,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="68">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46228.64583333334</v>
+        <v>46228.63541666666</v>
       </c>
     </row>
     <row r="69">
@@ -11331,27 +11331,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="O69" t="n">
-        <v>3.36</v>
+        <v>3.82</v>
       </c>
       <c r="P69" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,16 +11417,16 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46228.65625</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="70">
@@ -11490,27 +11490,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="71">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>46228.66666666666</v>
+        <v>46228.65625</v>
       </c>
     </row>
     <row r="73">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46228.70833333334</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>46228.70833333334</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="76">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>46228.75</v>
+        <v>46228.66666666666</v>
       </c>
     </row>
     <row r="77">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12753,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46228.70833333334</v>
       </c>
     </row>
     <row r="78">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.70833333334</v>
       </c>
     </row>
     <row r="79">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.75</v>
       </c>
     </row>
     <row r="80">
@@ -13080,12 +13080,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>46228.77083333334</v>
+        <v>46228.76041666666</v>
       </c>
     </row>
     <row r="81">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O82" t="n">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P82" t="n">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46228.79166666666</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="84">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>46228.79166666666</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="85">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13967,10 +13967,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46228.8125</v>
+        <v>46228.77083333334</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14126,10 +14126,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.79166666666</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O87" t="n">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="P87" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14273,16 +14273,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.79166666666</v>
       </c>
     </row>
     <row r="88">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14444,10 +14444,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46228.83333333334</v>
+        <v>46228.8125</v>
       </c>
     </row>
     <row r="89">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="O90" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="P90" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="O92" t="n">
-        <v>4.04</v>
+        <v>3.06</v>
       </c>
       <c r="P92" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="93">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="O93" t="n">
-        <v>4.18</v>
+        <v>3.95</v>
       </c>
       <c r="P93" t="n">
-        <v>2.15</v>
+        <v>4.9</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,16 +15233,16 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="94">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="O94" t="n">
-        <v>4.08</v>
+        <v>4.81</v>
       </c>
       <c r="P94" t="n">
-        <v>3.88</v>
+        <v>4.28</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,16 +15392,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46228.85416666666</v>
+        <v>46228.83333333334</v>
       </c>
     </row>
     <row r="95">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="O95" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="P95" t="n">
-        <v>4.28</v>
+        <v>3.11</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15667,17 +15667,17 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15716,10 +15716,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.95</v>
+        <v>1.96</v>
       </c>
       <c r="O98" t="n">
-        <v>4.53</v>
+        <v>3.36</v>
       </c>
       <c r="P98" t="n">
-        <v>2.12</v>
+        <v>4.28</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="O99" t="n">
-        <v>3.68</v>
+        <v>4.04</v>
       </c>
       <c r="P99" t="n">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16303,17 +16303,17 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46228.86458333334</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="101">
@@ -16419,27 +16419,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16511,10 +16511,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="102">
@@ -16578,27 +16578,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="AU102" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.85416666666</v>
       </c>
     </row>
     <row r="103">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="AU103" s="3" t="n">
-        <v>46228.875</v>
+        <v>46228.86458333334</v>
       </c>
     </row>
     <row r="104">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,22 +17060,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18486,12 +18486,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18533,13 +18533,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -18572,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -18636,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="AU114" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.875</v>
       </c>
     </row>
     <row r="115">
@@ -18645,12 +18645,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18692,13 +18692,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
         <v>0</v>
       </c>
       <c r="AU115" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46228.875</v>
       </c>
     </row>
     <row r="116">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19122,12 +19122,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19208,10 +19208,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="AU118" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="119">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="O119" t="n">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="P119" t="n">
-        <v>5</v>
+        <v>5.56</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19367,10 +19367,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="AU119" s="3" t="n">
-        <v>46228.91666666666</v>
+        <v>46228.89583333334</v>
       </c>
     </row>
     <row r="120">
@@ -19440,12 +19440,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="O120" t="n">
-        <v>4.01</v>
+        <v>4.4</v>
       </c>
       <c r="P120" t="n">
-        <v>3.23</v>
+        <v>5</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -19532,10 +19532,10 @@
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AU120" s="3" t="n">
-        <v>46228.9375</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="121">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19685,10 +19685,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -19749,7 +19749,7 @@
         <v>0</v>
       </c>
       <c r="AU121" s="3" t="n">
-        <v>46228.95833333334</v>
+        <v>46228.91666666666</v>
       </c>
     </row>
     <row r="122">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -19850,10 +19850,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="AU122" s="3" t="n">
-        <v>46228.95833333334</v>
+        <v>46228.9375</v>
       </c>
     </row>
     <row r="123">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20009,10 +20009,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -20067,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="AU123" s="3" t="n">
-        <v>46228.97916666666</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="124">
@@ -20076,12 +20076,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -20123,13 +20123,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="O124" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P124" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -20162,16 +20162,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -20226,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="AU124" s="3" t="n">
-        <v>46228.97916666666</v>
+        <v>46228.95833333334</v>
       </c>
     </row>
     <row r="125">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O125" t="n">
-        <v>7.95</v>
+        <v>4.65</v>
       </c>
       <c r="P125" t="n">
-        <v>12.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20327,10 +20327,10 @@
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -20399,151 +20399,469 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O126" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P126" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" s="3" t="n">
+        <v>46228.97916666666</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Hartford Athletic</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N126" t="n">
+      <c r="N127" t="n">
         <v>2.06</v>
       </c>
-      <c r="O126" t="n">
+      <c r="O127" t="n">
         <v>3.4</v>
       </c>
-      <c r="P126" t="n">
+      <c r="P127" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB126" t="n">
+      <c r="AB127" t="n">
         <v>1.92</v>
       </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU126" s="3" t="n">
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" s="3" t="n">
+        <v>46228.97916666666</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O128" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" s="3" t="n">
         <v>46228.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="O47" t="n">
-        <v>3.72</v>
+        <v>5.3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.32</v>
+        <v>6.06</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8402,10 +8402,10 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.56</v>
+        <v>3.31</v>
       </c>
       <c r="O52" t="n">
-        <v>3.78</v>
+        <v>3.26</v>
       </c>
       <c r="P52" t="n">
-        <v>5.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O53" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="P53" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.42</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4232,34 +4232,34 @@
         <v>3.69</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
         <v>1.92</v>
@@ -4268,19 +4268,19 @@
         <v>1.79</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>3.28</v>
+        <v>2.73</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.27</v>
+        <v>4.84</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="P27" t="n">
-        <v>2.73</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5027,55 +5027,55 @@
         <v>1.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="O40" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P42" t="n">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="O46" t="n">
-        <v>3.78</v>
+        <v>5.3</v>
       </c>
       <c r="P46" t="n">
-        <v>5.95</v>
+        <v>6.06</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.72</v>
+        <v>1.84</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P50" t="n">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.31</v>
+        <v>1.56</v>
       </c>
       <c r="O52" t="n">
-        <v>3.26</v>
+        <v>3.78</v>
       </c>
       <c r="P52" t="n">
-        <v>2.04</v>
+        <v>5.95</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="O66" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P66" t="n">
-        <v>6.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="P69" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,16 +11417,16 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O71" t="n">
-        <v>3.32</v>
+        <v>3.82</v>
       </c>
       <c r="P71" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,16 +11735,16 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.25</v>
+        <v>4.32</v>
       </c>
       <c r="O90" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="P90" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="O91" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="P91" t="n">
-        <v>3.92</v>
+        <v>4.9</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O92" t="n">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P92" t="n">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O93" t="n">
-        <v>3.95</v>
+        <v>4.81</v>
       </c>
       <c r="P93" t="n">
-        <v>4.9</v>
+        <v>4.28</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,16 +15233,16 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="O94" t="n">
-        <v>4.81</v>
+        <v>3.06</v>
       </c>
       <c r="P94" t="n">
-        <v>4.28</v>
+        <v>2.71</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15398,10 +15398,10 @@
         <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>1.96</v>
       </c>
       <c r="O96" t="n">
-        <v>4.53</v>
+        <v>3.36</v>
       </c>
       <c r="P96" t="n">
-        <v>2.12</v>
+        <v>4.28</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15716,10 +15716,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="O97" t="n">
-        <v>3.96</v>
+        <v>4.53</v>
       </c>
       <c r="P97" t="n">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,16 +15869,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O98" t="n">
-        <v>3.36</v>
+        <v>3.96</v>
       </c>
       <c r="P98" t="n">
-        <v>4.28</v>
+        <v>3.65</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16144,17 +16144,17 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16303,17 +16303,17 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="O102" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="P102" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -18851,13 +18851,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -18890,10 +18890,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3.41</v>
+        <v>2.3</v>
       </c>
       <c r="O117" t="n">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="P117" t="n">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19137,12 +19137,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="O118" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="P118" t="n">
-        <v>4.16</v>
+        <v>5.56</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -19208,10 +19208,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1.59</v>
+        <v>3.41</v>
       </c>
       <c r="O119" t="n">
-        <v>4.47</v>
+        <v>3.93</v>
       </c>
       <c r="P119" t="n">
-        <v>5.56</v>
+        <v>2.07</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -19367,10 +19367,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -19455,12 +19455,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="O120" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P120" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -19614,12 +19614,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20250,12 +20250,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20282,13 +20282,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="O125" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="P125" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -20321,16 +20321,16 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20600,13 +20600,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="O127" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P127" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -20639,16 +20639,16 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20759,13 +20759,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="O128" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="P128" t="n">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU124"/>
+  <dimension ref="A1:AU128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>8.85</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G15">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC20">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="AD20">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,34 +3904,34 @@
         <v>3.34</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
         <v>1.89</v>
@@ -3940,19 +3940,19 @@
         <v>1.81</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>3.69</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
         <v>1.92</v>
@@ -4266,19 +4266,19 @@
         <v>1.79</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>2.73</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>1.66</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>1.47</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>1.79</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G38">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>3.61</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10611,10 +10611,10 @@
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-07-25 15:15:00</t>
+          <t>2026-07-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-07-25 15:15:00</t>
+          <t>2026-07-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>5.1</v>
+        <v>1.48</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="P65">
-        <v>1.63</v>
+        <v>5.33</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,16 +10943,16 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-07-25 15:15:00</t>
+          <t>2026-07-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-07-25 15:30:00</t>
+          <t>2026-07-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.92</v>
+        <v>1.46</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P67">
-        <v>2.45</v>
+        <v>6.34</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-07-25 15:30:00</t>
+          <t>2026-07-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-07-25 15:30:00</t>
+          <t>2026-07-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-07-25 15:45:00</t>
+          <t>2026-07-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-07-25 16:00:00</t>
+          <t>2026-07-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-07-25 16:00:00</t>
+          <t>2026-07-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G72">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-07-25 16:00:00</t>
+          <t>2026-07-25 15:45:00</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G73">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-07-25 17:00:00</t>
+          <t>2026-07-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G75">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-07-25 17:00:00</t>
+          <t>2026-07-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12730,10 +12730,10 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-07-25 18:00:00</t>
+          <t>2026-07-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-07-25 18:15:00</t>
+          <t>2026-07-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-07-25 18:30:00</t>
+          <t>2026-07-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.52</v>
+        <v>4</v>
       </c>
       <c r="O79">
-        <v>4.29</v>
+        <v>3.58</v>
       </c>
       <c r="P79">
-        <v>6.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-07-25 18:30:00</t>
+          <t>2026-07-25 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-07-25 18:30:00</t>
+          <t>2026-07-25 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00:00</t>
+          <t>2026-07-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00:00</t>
+          <t>2026-07-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-07-25 19:30:00</t>
+          <t>2026-07-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-07-25 20:00:00</t>
+          <t>2026-07-25 19:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-07-25 20:00:00</t>
+          <t>2026-07-25 19:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14698,10 +14698,10 @@
         <v>0</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-07-25 20:00:00</t>
+          <t>2026-07-25 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="O92">
-        <v>3.36</v>
+        <v>3.95</v>
       </c>
       <c r="P92">
-        <v>4.28</v>
+        <v>4.9</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-07-25 20:30:00</t>
+          <t>2026-07-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,17 +15464,17 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-07-25 20:30:00</t>
+          <t>2026-07-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15676,10 +15676,10 @@
         <v>0</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-07-25 20:30:00</t>
+          <t>2026-07-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G96">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16328,10 +16328,10 @@
         <v>0</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-07-25 20:45:00</t>
+          <t>2026-07-25 20:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16817,10 +16817,10 @@
         <v>0</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 20:30:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 20:45:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G110">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 21:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 21:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-07-25 22:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-07-25 22:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-07-25 23:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-07-25 23:00:00</t>
+          <t>2026-07-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-07-25 23:30:00</t>
+          <t>2026-07-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20240,10 +20240,10 @@
         <v>0</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-07-25 23:30:00</t>
+          <t>2026-07-25 22:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-07-25 23:30:00</t>
+          <t>2026-07-25 23:00:00</t>
         </is>
       </c>
     </row>
@@ -20474,156 +20474,808 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N124">
+        <v>2.35</v>
+      </c>
+      <c r="O124">
+        <v>3.15</v>
+      </c>
+      <c r="P124">
+        <v>2.72</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <v>0</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
+      </c>
+      <c r="X124">
+        <v>0</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
+      </c>
+      <c r="Z124">
+        <v>0</v>
+      </c>
+      <c r="AA124">
+        <v>0</v>
+      </c>
+      <c r="AB124">
+        <v>0</v>
+      </c>
+      <c r="AC124">
+        <v>0</v>
+      </c>
+      <c r="AD124">
+        <v>0</v>
+      </c>
+      <c r="AE124">
+        <v>0</v>
+      </c>
+      <c r="AF124">
+        <v>0</v>
+      </c>
+      <c r="AG124">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
+        <v>0</v>
+      </c>
+      <c r="AK124">
+        <v>0</v>
+      </c>
+      <c r="AL124">
+        <v>0</v>
+      </c>
+      <c r="AM124">
+        <v>-1</v>
+      </c>
+      <c r="AN124">
+        <v>-1</v>
+      </c>
+      <c r="AO124">
+        <v>-1</v>
+      </c>
+      <c r="AP124">
+        <v>-1</v>
+      </c>
+      <c r="AQ124">
+        <v>0</v>
+      </c>
+      <c r="AR124">
+        <v>0</v>
+      </c>
+      <c r="AS124">
+        <v>0</v>
+      </c>
+      <c r="AT124">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>2026-07-25 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N125">
+        <v>2.06</v>
+      </c>
+      <c r="O125">
+        <v>3.4</v>
+      </c>
+      <c r="P125">
+        <v>3.1</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>0</v>
+      </c>
+      <c r="U125">
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <v>0</v>
+      </c>
+      <c r="W125">
+        <v>0</v>
+      </c>
+      <c r="X125">
+        <v>0</v>
+      </c>
+      <c r="Y125">
+        <v>0</v>
+      </c>
+      <c r="Z125">
+        <v>0</v>
+      </c>
+      <c r="AA125">
+        <v>1.76</v>
+      </c>
+      <c r="AB125">
+        <v>1.92</v>
+      </c>
+      <c r="AC125">
+        <v>0</v>
+      </c>
+      <c r="AD125">
+        <v>0</v>
+      </c>
+      <c r="AE125">
+        <v>0</v>
+      </c>
+      <c r="AF125">
+        <v>0</v>
+      </c>
+      <c r="AG125">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <v>0</v>
+      </c>
+      <c r="AK125">
+        <v>0</v>
+      </c>
+      <c r="AL125">
+        <v>0</v>
+      </c>
+      <c r="AM125">
+        <v>-1</v>
+      </c>
+      <c r="AN125">
+        <v>-1</v>
+      </c>
+      <c r="AO125">
+        <v>-1</v>
+      </c>
+      <c r="AP125">
+        <v>-1</v>
+      </c>
+      <c r="AQ125">
+        <v>0</v>
+      </c>
+      <c r="AR125">
+        <v>0</v>
+      </c>
+      <c r="AS125">
+        <v>0</v>
+      </c>
+      <c r="AT125">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>2026-07-25 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N126">
+        <v>1.21</v>
+      </c>
+      <c r="O126">
+        <v>7.95</v>
+      </c>
+      <c r="P126">
+        <v>12.7</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126">
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <v>0</v>
+      </c>
+      <c r="W126">
+        <v>0</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+      <c r="AA126">
+        <v>0</v>
+      </c>
+      <c r="AB126">
+        <v>0</v>
+      </c>
+      <c r="AC126">
+        <v>1.71</v>
+      </c>
+      <c r="AD126">
+        <v>1.98</v>
+      </c>
+      <c r="AE126">
+        <v>0</v>
+      </c>
+      <c r="AF126">
+        <v>0</v>
+      </c>
+      <c r="AG126">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>0</v>
+      </c>
+      <c r="AK126">
+        <v>0</v>
+      </c>
+      <c r="AL126">
+        <v>0</v>
+      </c>
+      <c r="AM126">
+        <v>-1</v>
+      </c>
+      <c r="AN126">
+        <v>-1</v>
+      </c>
+      <c r="AO126">
+        <v>-1</v>
+      </c>
+      <c r="AP126">
+        <v>-1</v>
+      </c>
+      <c r="AQ126">
+        <v>0</v>
+      </c>
+      <c r="AR126">
+        <v>0</v>
+      </c>
+      <c r="AS126">
+        <v>0</v>
+      </c>
+      <c r="AT126">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>2026-07-25 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N127">
+        <v>2.36</v>
+      </c>
+      <c r="O127">
+        <v>4.3</v>
+      </c>
+      <c r="P127">
+        <v>2.67</v>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127">
+        <v>0</v>
+      </c>
+      <c r="V127">
+        <v>0</v>
+      </c>
+      <c r="W127">
+        <v>0</v>
+      </c>
+      <c r="X127">
+        <v>0</v>
+      </c>
+      <c r="Y127">
+        <v>0</v>
+      </c>
+      <c r="Z127">
+        <v>0</v>
+      </c>
+      <c r="AA127">
+        <v>0</v>
+      </c>
+      <c r="AB127">
+        <v>0</v>
+      </c>
+      <c r="AC127">
+        <v>2.05</v>
+      </c>
+      <c r="AD127">
+        <v>1.66</v>
+      </c>
+      <c r="AE127">
+        <v>0</v>
+      </c>
+      <c r="AF127">
+        <v>0</v>
+      </c>
+      <c r="AG127">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>0</v>
+      </c>
+      <c r="AK127">
+        <v>0</v>
+      </c>
+      <c r="AL127">
+        <v>0</v>
+      </c>
+      <c r="AM127">
+        <v>-1</v>
+      </c>
+      <c r="AN127">
+        <v>-1</v>
+      </c>
+      <c r="AO127">
+        <v>-1</v>
+      </c>
+      <c r="AP127">
+        <v>-1</v>
+      </c>
+      <c r="AQ127">
+        <v>0</v>
+      </c>
+      <c r="AR127">
+        <v>0</v>
+      </c>
+      <c r="AS127">
+        <v>0</v>
+      </c>
+      <c r="AT127">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>2026-07-25 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
+      <c r="N128">
+        <v>1.71</v>
+      </c>
+      <c r="O128">
+        <v>4.65</v>
+      </c>
+      <c r="P128">
+        <v>4.33</v>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
+        <v>0</v>
+      </c>
+      <c r="Z128">
+        <v>0</v>
+      </c>
+      <c r="AA128">
+        <v>0</v>
+      </c>
+      <c r="AB128">
+        <v>0</v>
+      </c>
+      <c r="AC128">
+        <v>2.05</v>
+      </c>
+      <c r="AD128">
+        <v>1.66</v>
+      </c>
+      <c r="AE128">
+        <v>0</v>
+      </c>
+      <c r="AF128">
+        <v>0</v>
+      </c>
+      <c r="AG128">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>0</v>
+      </c>
+      <c r="AK128">
+        <v>0</v>
+      </c>
+      <c r="AL128">
+        <v>0</v>
+      </c>
+      <c r="AM128">
+        <v>-1</v>
+      </c>
+      <c r="AN128">
+        <v>-1</v>
+      </c>
+      <c r="AO128">
+        <v>-1</v>
+      </c>
+      <c r="AP128">
+        <v>-1</v>
+      </c>
+      <c r="AQ128">
+        <v>0</v>
+      </c>
+      <c r="AR128">
+        <v>0</v>
+      </c>
+      <c r="AS128">
+        <v>0</v>
+      </c>
+      <c r="AT128">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-07-25 23:30:00</t>
         </is>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.42</v>
+        <v>2.31</v>
       </c>
       <c r="O12">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="P12">
-        <v>2.07</v>
+        <v>2.86</v>
       </c>
       <c r="Q12">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
+        <v>1.03</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.31</v>
+      </c>
+      <c r="Z12">
+        <v>2.92</v>
+      </c>
+      <c r="AA12">
+        <v>2.04</v>
+      </c>
+      <c r="AB12">
+        <v>1.71</v>
+      </c>
+      <c r="AC12">
+        <v>3.58</v>
+      </c>
+      <c r="AD12">
+        <v>1.21</v>
+      </c>
+      <c r="AE12">
         <v>1.04</v>
       </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>1.25</v>
-      </c>
-      <c r="Z12">
-        <v>3.77</v>
-      </c>
-      <c r="AA12">
-        <v>1.85</v>
-      </c>
-      <c r="AB12">
-        <v>1.84</v>
-      </c>
-      <c r="AC12">
-        <v>2.92</v>
-      </c>
-      <c r="AD12">
-        <v>1.31</v>
-      </c>
-      <c r="AE12">
-        <v>1.08</v>
-      </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.31</v>
+        <v>3.42</v>
       </c>
       <c r="O13">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="P13">
-        <v>2.86</v>
+        <v>2.07</v>
       </c>
       <c r="Q13">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="U13">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.77</v>
+      </c>
+      <c r="AA13">
+        <v>1.85</v>
+      </c>
+      <c r="AB13">
+        <v>1.84</v>
+      </c>
+      <c r="AC13">
+        <v>2.92</v>
+      </c>
+      <c r="AD13">
         <v>1.31</v>
       </c>
-      <c r="Z13">
-        <v>2.92</v>
-      </c>
-      <c r="AA13">
-        <v>2.04</v>
-      </c>
-      <c r="AB13">
-        <v>1.71</v>
-      </c>
-      <c r="AC13">
-        <v>3.58</v>
-      </c>
-      <c r="AD13">
-        <v>1.21</v>
-      </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -7164,55 +7164,55 @@
         <v>2.97</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>3.86</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.72</v>
+        <v>1.84</v>
       </c>
       <c r="O46">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P46">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD46">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="O47">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P47">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA47">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB47">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>2.07</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8468,34 +8468,34 @@
         <v>2.04</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA50">
         <v>1.84</v>
@@ -8504,19 +8504,19 @@
         <v>1.84</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>5.95</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G57">
@@ -9935,40 +9935,40 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC59">
         <v>1.92</v>
@@ -9977,13 +9977,13 @@
         <v>1.8</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10587,28 +10587,28 @@
         <v>5.67</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y63">
         <v>1.63</v>
@@ -10617,25 +10617,25 @@
         <v>2.1</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,40 +10913,40 @@
         <v>5.33</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC65">
         <v>1.9</v>
@@ -10955,13 +10955,13 @@
         <v>1.9</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>6.34</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>1.63</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA68">
         <v>1.95</v>
@@ -11438,19 +11438,19 @@
         <v>1.85</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,40 +11565,40 @@
         <v>2.43</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC69">
         <v>1.81</v>
@@ -11607,13 +11607,13 @@
         <v>1.91</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11891,34 +11891,34 @@
         <v>2.5</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA71">
         <v>1.74</v>
@@ -11927,19 +11927,19 @@
         <v>1.94</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,34 +12054,34 @@
         <v>2.69</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA72">
         <v>1.78</v>
@@ -12090,19 +12090,19 @@
         <v>1.88</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12706,28 +12706,28 @@
         <v>3.75</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y76">
         <v>1.65</v>
@@ -12736,25 +12736,25 @@
         <v>2.1</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>3.98</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14499,28 +14499,28 @@
         <v>4.35</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y87">
         <v>1.65</v>
@@ -14529,25 +14529,25 @@
         <v>2.1</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,40 +14662,40 @@
         <v>2.92</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC88">
         <v>2.25</v>
@@ -14704,13 +14704,13 @@
         <v>1.57</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>1.67</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>2.71</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,34 +15314,34 @@
         <v>4.9</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA92">
         <v>1.83</v>
@@ -15350,19 +15350,19 @@
         <v>1.93</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>3.92</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,40 +15640,40 @@
         <v>4.28</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AC94">
         <v>1.85</v>
@@ -15682,13 +15682,13 @@
         <v>1.82</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>4.28</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>3.05</v>
+      </c>
+      <c r="O97">
+        <v>4.18</v>
+      </c>
+      <c r="P97">
+        <v>2.15</v>
+      </c>
+      <c r="Q97">
+        <v>3.5</v>
+      </c>
+      <c r="R97">
         <v>2.38</v>
       </c>
-      <c r="O97">
-        <v>4.04</v>
-      </c>
-      <c r="P97">
-        <v>2.75</v>
-      </c>
-      <c r="Q97">
-        <v>0</v>
-      </c>
-      <c r="R97">
-        <v>0</v>
-      </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA97">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
+        <v>1.89</v>
+      </c>
+      <c r="O98">
+        <v>4.08</v>
+      </c>
+      <c r="P98">
+        <v>3.88</v>
+      </c>
+      <c r="Q98">
+        <v>2.45</v>
+      </c>
+      <c r="R98">
+        <v>2.3</v>
+      </c>
+      <c r="S98">
+        <v>1.33</v>
+      </c>
+      <c r="T98">
         <v>3.05</v>
       </c>
-      <c r="O98">
-        <v>4.18</v>
-      </c>
-      <c r="P98">
-        <v>2.15</v>
-      </c>
-      <c r="Q98">
-        <v>0</v>
-      </c>
-      <c r="R98">
-        <v>0</v>
-      </c>
-      <c r="S98">
-        <v>0</v>
-      </c>
-      <c r="T98">
-        <v>0</v>
-      </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC98">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="O99">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="P99">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="O100">
-        <v>3.96</v>
+        <v>4.53</v>
       </c>
       <c r="P100">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,16 +16648,16 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB100">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.95</v>
+        <v>2.29</v>
       </c>
       <c r="O101">
-        <v>4.53</v>
+        <v>3.68</v>
       </c>
       <c r="P101">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC101">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AD101">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="O102">
-        <v>3.68</v>
+        <v>4.04</v>
       </c>
       <c r="P102">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA102">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,34 +17107,34 @@
         <v>3.04</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA103">
         <v>1.76</v>
@@ -17143,19 +17143,19 @@
         <v>1.9</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>2.66</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,34 +19389,34 @@
         <v>4.16</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA117">
         <v>1.55</v>
@@ -19425,19 +19425,19 @@
         <v>2.25</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,34 +19552,34 @@
         <v>5.56</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA118">
         <v>1.58</v>
@@ -19588,19 +19588,19 @@
         <v>2.2</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,34 +19715,34 @@
         <v>2.07</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA119">
         <v>1.55</v>
@@ -19751,19 +19751,19 @@
         <v>2.25</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>2.5</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>5</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,40 +20204,40 @@
         <v>3.23</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X122">
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC122">
         <v>1.98</v>
@@ -20246,13 +20246,13 @@
         <v>1.72</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20367,34 +20367,34 @@
         <v>3.2</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA123">
         <v>1.79</v>
@@ -20403,19 +20403,19 @@
         <v>1.88</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20530,55 +20530,55 @@
         <v>2.72</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,34 +20693,34 @@
         <v>3.1</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA125">
         <v>1.76</v>
@@ -20729,19 +20729,19 @@
         <v>1.92</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,40 +20856,40 @@
         <v>12.7</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X126">
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AC126">
         <v>1.71</v>
@@ -20898,13 +20898,13 @@
         <v>1.98</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21019,40 +21019,40 @@
         <v>2.67</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X127">
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC127">
         <v>2.05</v>
@@ -21061,13 +21061,13 @@
         <v>1.66</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,40 +21182,40 @@
         <v>4.33</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X128">
         <v>0</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC128">
         <v>2.05</v>
@@ -21224,13 +21224,13 @@
         <v>1.66</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="O82">
-        <v>3.34</v>
+        <v>4.29</v>
       </c>
       <c r="P82">
-        <v>3.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AB82">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC82">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,65 +13838,65 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="O83">
-        <v>4.29</v>
+        <v>3.34</v>
       </c>
       <c r="P83">
-        <v>6.63</v>
+        <v>3.98</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA83">
+        <v>2.38</v>
+      </c>
+      <c r="AB83">
+        <v>1.57</v>
+      </c>
+      <c r="AC83">
+        <v>4.6</v>
+      </c>
+      <c r="AD83">
+        <v>1.2</v>
+      </c>
+      <c r="AE83">
+        <v>1.03</v>
+      </c>
+      <c r="AF83">
+        <v>2.01</v>
+      </c>
+      <c r="AG83">
         <v>1.72</v>
       </c>
-      <c r="AB83">
-        <v>2.07</v>
-      </c>
-      <c r="AC83">
-        <v>0</v>
-      </c>
-      <c r="AD83">
-        <v>0</v>
-      </c>
-      <c r="AE83">
-        <v>0</v>
-      </c>
-      <c r="AF83">
-        <v>0</v>
-      </c>
-      <c r="AG83">
-        <v>0</v>
-      </c>
       <c r="AH83" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>4.32</v>
+        <v>1.53</v>
       </c>
       <c r="O90">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="P90">
-        <v>1.67</v>
+        <v>4.9</v>
       </c>
       <c r="Q90">
-        <v>4.78</v>
+        <v>2.09</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T90">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U90">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="V90">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W90">
+        <v>1.08</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>1.2</v>
+      </c>
+      <c r="Z90">
+        <v>3.68</v>
+      </c>
+      <c r="AA90">
+        <v>1.83</v>
+      </c>
+      <c r="AB90">
+        <v>1.93</v>
+      </c>
+      <c r="AC90">
+        <v>2.74</v>
+      </c>
+      <c r="AD90">
+        <v>1.35</v>
+      </c>
+      <c r="AE90">
         <v>1.11</v>
       </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.16</v>
-      </c>
-      <c r="Z90">
-        <v>3.94</v>
-      </c>
-      <c r="AA90">
-        <v>1.54</v>
-      </c>
-      <c r="AB90">
-        <v>2.07</v>
-      </c>
-      <c r="AC90">
-        <v>2.62</v>
-      </c>
-      <c r="AD90">
-        <v>1.38</v>
-      </c>
-      <c r="AE90">
-        <v>1.12</v>
-      </c>
       <c r="AF90">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.14</v>
+        <v>2.19</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O91">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P91">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="R91">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="S91">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="T91">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.52</v>
       </c>
       <c r="V91">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W91">
+        <v>1.09</v>
+      </c>
+      <c r="X91">
         <v>1.02</v>
       </c>
-      <c r="X91">
-        <v>1.04</v>
-      </c>
       <c r="Y91">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="Z91">
-        <v>2.66</v>
+        <v>4.15</v>
       </c>
       <c r="AA91">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="AB91">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD91">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AG91">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK91">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.53</v>
+        <v>4.32</v>
       </c>
       <c r="O92">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="P92">
-        <v>4.9</v>
+        <v>1.67</v>
       </c>
       <c r="Q92">
-        <v>2.09</v>
+        <v>4.78</v>
       </c>
       <c r="R92">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="V92">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z92">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="AA92">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="AB92">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC92">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD92">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK92">
-        <v>2.19</v>
+        <v>1.14</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.71</v>
+        <v>2.41</v>
       </c>
       <c r="O93">
-        <v>3.86</v>
+        <v>3.06</v>
       </c>
       <c r="P93">
-        <v>3.92</v>
+        <v>2.71</v>
       </c>
       <c r="Q93">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="R93">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="S93">
+        <v>1.47</v>
+      </c>
+      <c r="T93">
+        <v>2.6</v>
+      </c>
+      <c r="U93">
+        <v>3.12</v>
+      </c>
+      <c r="V93">
         <v>1.29</v>
       </c>
-      <c r="T93">
-        <v>3.25</v>
-      </c>
-      <c r="U93">
-        <v>2.52</v>
-      </c>
-      <c r="V93">
-        <v>1.53</v>
-      </c>
       <c r="W93">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X93">
+        <v>1.04</v>
+      </c>
+      <c r="Y93">
+        <v>1.37</v>
+      </c>
+      <c r="Z93">
+        <v>2.66</v>
+      </c>
+      <c r="AA93">
+        <v>2.29</v>
+      </c>
+      <c r="AB93">
+        <v>1.6</v>
+      </c>
+      <c r="AC93">
+        <v>4.2</v>
+      </c>
+      <c r="AD93">
+        <v>1.2</v>
+      </c>
+      <c r="AE93">
         <v>1.02</v>
       </c>
-      <c r="Y93">
-        <v>1.16</v>
-      </c>
-      <c r="Z93">
-        <v>4.15</v>
-      </c>
-      <c r="AA93">
-        <v>1.65</v>
-      </c>
-      <c r="AB93">
-        <v>2.15</v>
-      </c>
-      <c r="AC93">
-        <v>2.52</v>
-      </c>
-      <c r="AD93">
-        <v>1.41</v>
-      </c>
-      <c r="AE93">
-        <v>1.13</v>
-      </c>
       <c r="AF93">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AG93">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>1.89</v>
+      </c>
+      <c r="O97">
+        <v>4.08</v>
+      </c>
+      <c r="P97">
+        <v>3.88</v>
+      </c>
+      <c r="Q97">
+        <v>2.45</v>
+      </c>
+      <c r="R97">
+        <v>2.3</v>
+      </c>
+      <c r="S97">
+        <v>1.33</v>
+      </c>
+      <c r="T97">
         <v>3.05</v>
       </c>
-      <c r="O97">
-        <v>4.18</v>
-      </c>
-      <c r="P97">
-        <v>2.15</v>
-      </c>
-      <c r="Q97">
-        <v>3.5</v>
-      </c>
-      <c r="R97">
-        <v>2.38</v>
-      </c>
-      <c r="S97">
-        <v>1.25</v>
-      </c>
-      <c r="T97">
-        <v>3.75</v>
-      </c>
       <c r="U97">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="V97">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W97">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB97">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC97">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD97">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AE97">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF97">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AG97">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="O98">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="P98">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q98">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T98">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U98">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V98">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y98">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z98">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD98">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG98">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK98">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="O99">
-        <v>3.96</v>
+        <v>4.53</v>
       </c>
       <c r="P99">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,16 +16485,16 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.95</v>
+        <v>2.29</v>
       </c>
       <c r="O100">
-        <v>4.53</v>
+        <v>3.68</v>
       </c>
       <c r="P100">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC100">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AD100">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="O101">
-        <v>3.68</v>
+        <v>4.04</v>
       </c>
       <c r="P101">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="Q101">
         <v>2.8</v>
       </c>
       <c r="R101">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T101">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U101">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W101">
         <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA101">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB101">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC101">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="AD101">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AE101">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG101">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,34 +16935,34 @@
         </is>
       </c>
       <c r="N102">
+        <v>3.05</v>
+      </c>
+      <c r="O102">
+        <v>4.18</v>
+      </c>
+      <c r="P102">
+        <v>2.15</v>
+      </c>
+      <c r="Q102">
+        <v>3.5</v>
+      </c>
+      <c r="R102">
         <v>2.38</v>
       </c>
-      <c r="O102">
-        <v>4.04</v>
-      </c>
-      <c r="P102">
-        <v>2.75</v>
-      </c>
-      <c r="Q102">
-        <v>2.8</v>
-      </c>
-      <c r="R102">
-        <v>2.35</v>
-      </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U102">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="V102">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -16971,28 +16971,28 @@
         <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB102">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC102">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AD102">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AE102">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF102">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG102">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK102">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL102">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O120">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P120">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Q120">
-        <v>2.86</v>
+        <v>1.87</v>
       </c>
       <c r="R120">
-        <v>2.23</v>
+        <v>2.67</v>
       </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T120">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="U120">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W120">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z120">
-        <v>3.92</v>
+        <v>5.04</v>
       </c>
       <c r="AA120">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AB120">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC120">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD120">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE120">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF120">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AG120">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AK120">
-        <v>1.47</v>
+        <v>2.57</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="O121">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q121">
-        <v>1.87</v>
+        <v>2.86</v>
       </c>
       <c r="R121">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
       <c r="S121">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T121">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U121">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V121">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W121">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z121">
-        <v>5.04</v>
+        <v>3.92</v>
       </c>
       <c r="AA121">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AB121">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC121">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD121">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE121">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF121">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG121">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AK121">
-        <v>2.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,34 +21010,34 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="O127">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="P127">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="Q127">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="R127">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S127">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T127">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U127">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V127">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W127">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X127">
         <v>0</v>
@@ -21049,10 +21049,10 @@
         <v>6</v>
       </c>
       <c r="AA127">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB127">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC127">
         <v>2.05</v>
@@ -21061,13 +21061,13 @@
         <v>1.66</v>
       </c>
       <c r="AE127">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF127">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG127">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK127">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.71</v>
+        <v>2.36</v>
       </c>
       <c r="O128">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="P128">
-        <v>4.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q128">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="R128">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S128">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T128">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U128">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V128">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W128">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>6</v>
       </c>
       <c r="AA128">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB128">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
         <v>2.05</v>
@@ -21224,13 +21224,13 @@
         <v>1.66</v>
       </c>
       <c r="AE128">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF128">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG128">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.71</v>
+        <v>4.32</v>
       </c>
       <c r="O91">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="P91">
-        <v>3.92</v>
+        <v>1.67</v>
       </c>
       <c r="Q91">
-        <v>2.15</v>
+        <v>4.78</v>
       </c>
       <c r="R91">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S91">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T91">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U91">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="V91">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W91">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
         <v>1.16</v>
       </c>
       <c r="Z91">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AA91">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB91">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC91">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
+        <v>1.19</v>
+      </c>
+      <c r="AK91">
         <v>1.14</v>
-      </c>
-      <c r="AK91">
-        <v>1.72</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>4.32</v>
+        <v>2.41</v>
       </c>
       <c r="O92">
-        <v>3.72</v>
+        <v>3.06</v>
       </c>
       <c r="P92">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="Q92">
-        <v>4.78</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S92">
+        <v>1.47</v>
+      </c>
+      <c r="T92">
+        <v>2.6</v>
+      </c>
+      <c r="U92">
+        <v>3.12</v>
+      </c>
+      <c r="V92">
+        <v>1.29</v>
+      </c>
+      <c r="W92">
+        <v>1.02</v>
+      </c>
+      <c r="X92">
+        <v>1.04</v>
+      </c>
+      <c r="Y92">
+        <v>1.37</v>
+      </c>
+      <c r="Z92">
+        <v>2.66</v>
+      </c>
+      <c r="AA92">
+        <v>2.29</v>
+      </c>
+      <c r="AB92">
+        <v>1.6</v>
+      </c>
+      <c r="AC92">
+        <v>4.2</v>
+      </c>
+      <c r="AD92">
+        <v>1.2</v>
+      </c>
+      <c r="AE92">
+        <v>1.02</v>
+      </c>
+      <c r="AF92">
+        <v>1.89</v>
+      </c>
+      <c r="AG92">
+        <v>1.8</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.3</v>
       </c>
-      <c r="T92">
-        <v>3.2</v>
-      </c>
-      <c r="U92">
-        <v>2.41</v>
-      </c>
-      <c r="V92">
-        <v>1.5</v>
-      </c>
-      <c r="W92">
-        <v>1.11</v>
-      </c>
-      <c r="X92">
-        <v>1.01</v>
-      </c>
-      <c r="Y92">
-        <v>1.16</v>
-      </c>
-      <c r="Z92">
-        <v>3.94</v>
-      </c>
-      <c r="AA92">
-        <v>1.54</v>
-      </c>
-      <c r="AB92">
-        <v>2.07</v>
-      </c>
-      <c r="AC92">
-        <v>2.62</v>
-      </c>
-      <c r="AD92">
-        <v>1.38</v>
-      </c>
-      <c r="AE92">
-        <v>1.12</v>
-      </c>
-      <c r="AF92">
-        <v>1.62</v>
-      </c>
-      <c r="AG92">
-        <v>2.1</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.19</v>
-      </c>
       <c r="AK92">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O93">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P93">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q93">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="R93">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="S93">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="U93">
-        <v>3.12</v>
+        <v>2.52</v>
       </c>
       <c r="V93">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W93">
+        <v>1.09</v>
+      </c>
+      <c r="X93">
         <v>1.02</v>
       </c>
-      <c r="X93">
-        <v>1.04</v>
-      </c>
       <c r="Y93">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="Z93">
-        <v>2.66</v>
+        <v>4.15</v>
       </c>
       <c r="AA93">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="AB93">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD93">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AG93">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK93">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AL93">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="O36">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="Q36">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S36">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
         <v>1.03</v>
       </c>
-      <c r="X36">
+      <c r="Y36">
+        <v>1.32</v>
+      </c>
+      <c r="Z36">
+        <v>2.88</v>
+      </c>
+      <c r="AA36">
+        <v>2.09</v>
+      </c>
+      <c r="AB36">
+        <v>1.7</v>
+      </c>
+      <c r="AC36">
+        <v>3.5</v>
+      </c>
+      <c r="AD36">
+        <v>1.22</v>
+      </c>
+      <c r="AE36">
         <v>1.04</v>
       </c>
-      <c r="Y36">
-        <v>1.3</v>
-      </c>
-      <c r="Z36">
-        <v>3.2</v>
-      </c>
-      <c r="AA36">
-        <v>1.97</v>
-      </c>
-      <c r="AB36">
-        <v>1.73</v>
-      </c>
-      <c r="AC36">
-        <v>3.14</v>
-      </c>
-      <c r="AD36">
-        <v>1.27</v>
-      </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
       <c r="AF36">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-07-25 12:00:00</t>
+          <t>2026-07-25 11:30:00</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.5</v>
+        <v>2.36</v>
       </c>
       <c r="O37">
-        <v>4.1</v>
+        <v>2.91</v>
       </c>
       <c r="P37">
-        <v>5.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>3.06</v>
       </c>
       <c r="R37">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="T37">
-        <v>3.24</v>
+        <v>2.47</v>
       </c>
       <c r="U37">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AB37">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AC37">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AD37">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE37">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-07-25 12:30:00</t>
+          <t>2026-07-25 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="O41">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="P41">
-        <v>2.69</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AB41">
         <v>1.93</v>
       </c>
       <c r="AC41">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P42">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="Q42">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R42">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="V42">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>2.57</v>
+        <v>3.44</v>
       </c>
       <c r="AA42">
-        <v>2.64</v>
+        <v>1.84</v>
       </c>
       <c r="AB42">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>5.12</v>
+        <v>2.89</v>
       </c>
       <c r="AD42">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O43">
         <v>3.3</v>
       </c>
       <c r="P43">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R43">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S43">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="T43">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="U43">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z43">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AA43">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="AB43">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC43">
-        <v>3.5</v>
+        <v>5.12</v>
       </c>
       <c r="AD43">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G57">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.35</v>
+        <v>2.92</v>
       </c>
       <c r="O59">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>9.550000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="Q59">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>2.1</v>
+      </c>
+      <c r="AB59">
         <v>1.7</v>
       </c>
-      <c r="W59">
-        <v>1.16</v>
-      </c>
-      <c r="X59">
-        <v>1.01</v>
-      </c>
-      <c r="Y59">
-        <v>1.08</v>
-      </c>
-      <c r="Z59">
-        <v>5.36</v>
-      </c>
-      <c r="AA59">
-        <v>1.42</v>
-      </c>
-      <c r="AB59">
-        <v>2.66</v>
-      </c>
       <c r="AC59">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF59">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG59">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK59">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-07-25 14:45:00</t>
+          <t>2026-07-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-07-25 15:00:00</t>
+          <t>2026-07-25 14:45:00</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="P64">
-        <v>1.61</v>
+        <v>5.67</v>
       </c>
       <c r="Q64">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="S64">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="U64">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="V64">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="W64">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="Z64">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA64">
-        <v>1.68</v>
+        <v>2.87</v>
       </c>
       <c r="AB64">
-        <v>2.12</v>
+        <v>1.4</v>
       </c>
       <c r="AC64">
-        <v>2.56</v>
+        <v>5.9</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.69</v>
+        <v>2.67</v>
       </c>
       <c r="AG64">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
+        <v>4.8</v>
+      </c>
+      <c r="O65">
+        <v>3.6</v>
+      </c>
+      <c r="P65">
+        <v>1.61</v>
+      </c>
+      <c r="Q65">
+        <v>5</v>
+      </c>
+      <c r="R65">
+        <v>2.3</v>
+      </c>
+      <c r="S65">
+        <v>1.29</v>
+      </c>
+      <c r="T65">
+        <v>3.3</v>
+      </c>
+      <c r="U65">
+        <v>2.44</v>
+      </c>
+      <c r="V65">
         <v>1.48</v>
       </c>
-      <c r="O65">
-        <v>4.75</v>
-      </c>
-      <c r="P65">
-        <v>5.33</v>
-      </c>
-      <c r="Q65">
-        <v>2.09</v>
-      </c>
-      <c r="R65">
-        <v>2.55</v>
-      </c>
-      <c r="S65">
-        <v>1.17</v>
-      </c>
-      <c r="T65">
-        <v>4.1</v>
-      </c>
-      <c r="U65">
-        <v>1.99</v>
-      </c>
-      <c r="V65">
-        <v>1.75</v>
-      </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA65">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB65">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC65">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD65">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AG65">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11020,27 +11020,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-07-25 15:15:00</t>
+          <t>2026-07-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,61 +11393,61 @@
         </is>
       </c>
       <c r="N68">
-        <v>5.1</v>
+        <v>1.46</v>
       </c>
       <c r="O68">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="P68">
-        <v>1.63</v>
+        <v>6.34</v>
       </c>
       <c r="Q68">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="R68">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U68">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V68">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
         <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z68">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB68">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AC68">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AD68">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF68">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG68">
         <v>1.9</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>2.52</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>1.09</v>
+        <v>2.55</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.51</v>
+        <v>5.1</v>
       </c>
       <c r="O69">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
-        <v>2.43</v>
+        <v>1.63</v>
       </c>
       <c r="Q69">
+        <v>6</v>
+      </c>
+      <c r="R69">
+        <v>2.27</v>
+      </c>
+      <c r="S69">
+        <v>1.35</v>
+      </c>
+      <c r="T69">
+        <v>2.87</v>
+      </c>
+      <c r="U69">
+        <v>2.46</v>
+      </c>
+      <c r="V69">
+        <v>1.46</v>
+      </c>
+      <c r="W69">
+        <v>1.07</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.22</v>
+      </c>
+      <c r="Z69">
+        <v>3.9</v>
+      </c>
+      <c r="AA69">
+        <v>1.95</v>
+      </c>
+      <c r="AB69">
+        <v>1.85</v>
+      </c>
+      <c r="AC69">
         <v>2.73</v>
       </c>
-      <c r="R69">
-        <v>2.39</v>
-      </c>
-      <c r="S69">
-        <v>1.2</v>
-      </c>
-      <c r="T69">
-        <v>3.88</v>
-      </c>
-      <c r="U69">
-        <v>2</v>
-      </c>
-      <c r="V69">
-        <v>1.76</v>
-      </c>
-      <c r="W69">
-        <v>1.17</v>
-      </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.07</v>
-      </c>
-      <c r="Z69">
-        <v>6.21</v>
-      </c>
-      <c r="AA69">
-        <v>1.35</v>
-      </c>
-      <c r="AB69">
-        <v>2.87</v>
-      </c>
-      <c r="AC69">
+      <c r="AD69">
+        <v>1.42</v>
+      </c>
+      <c r="AE69">
+        <v>1.15</v>
+      </c>
+      <c r="AF69">
         <v>1.81</v>
       </c>
-      <c r="AD69">
-        <v>1.91</v>
-      </c>
-      <c r="AE69">
-        <v>1.3</v>
-      </c>
-      <c r="AF69">
-        <v>1.34</v>
-      </c>
       <c r="AG69">
-        <v>2.99</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.22</v>
+        <v>2.52</v>
       </c>
       <c r="AK69">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-07-25 15:30:00</t>
+          <t>2026-07-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P70">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="O105">
-        <v>4.35</v>
+        <v>3.23</v>
       </c>
       <c r="P105">
-        <v>6.29</v>
+        <v>3.69</v>
       </c>
       <c r="Q105">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC105">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G107">
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="O111">
-        <v>3.35</v>
+        <v>3.93</v>
       </c>
       <c r="P111">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="O112">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P112">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P113">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X114">
         <v>0</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 22:30:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-07-25 21:00:00</t>
+          <t>2026-07-25 23:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O116">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="P116">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q116">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R116">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S116">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U116">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="V116">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AA116">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AB116">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AC116">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="AD116">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG116">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AK116">
         <v>1.46</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 23:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="O117">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="P117">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q117">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="R117">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T117">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z117">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="AA117">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AB117">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC117">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD117">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AE117">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AG117">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK117">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 23:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="O118">
-        <v>4.47</v>
+        <v>7.95</v>
       </c>
       <c r="P118">
-        <v>5.56</v>
+        <v>12.7</v>
       </c>
       <c r="Q118">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R118">
-        <v>2.4</v>
+        <v>3.13</v>
       </c>
       <c r="S118">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="T118">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="U118">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="V118">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z118">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AA118">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AB118">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="AC118">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="AD118">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AE118">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AF118">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG118">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK118">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 23:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.41</v>
+        <v>1.71</v>
       </c>
       <c r="O119">
-        <v>3.93</v>
+        <v>4.65</v>
       </c>
       <c r="P119">
-        <v>2.07</v>
+        <v>4.33</v>
       </c>
       <c r="Q119">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="R119">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S119">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T119">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U119">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V119">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W119">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA119">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB119">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC119">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AD119">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AE119">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF119">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG119">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-07-25 21:30:00</t>
+          <t>2026-07-25 23:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,81 +19869,81 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.46</v>
+        <v>2.36</v>
       </c>
       <c r="O120">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P120">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q120">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="R120">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S120">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T120">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="U120">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V120">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="W120">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y120">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z120">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="AA120">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AB120">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="AC120">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD120">
+        <v>1.66</v>
+      </c>
+      <c r="AE120">
+        <v>1.25</v>
+      </c>
+      <c r="AF120">
+        <v>1.36</v>
+      </c>
+      <c r="AG120">
+        <v>2.88</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.25</v>
+      </c>
+      <c r="AK120">
         <v>1.57</v>
       </c>
-      <c r="AE120">
-        <v>1.19</v>
-      </c>
-      <c r="AF120">
-        <v>1.63</v>
-      </c>
-      <c r="AG120">
-        <v>2.12</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.12</v>
-      </c>
-      <c r="AK120">
-        <v>2.57</v>
-      </c>
       <c r="AL120">
         <v>0</v>
       </c>
@@ -19972,1310 +19972,6 @@
         <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
-        <is>
-          <t>2026-07-25 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Colorado Springs</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Charleston Battery</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N121">
-        <v>2.38</v>
-      </c>
-      <c r="O121">
-        <v>3.45</v>
-      </c>
-      <c r="P121">
-        <v>2.5</v>
-      </c>
-      <c r="Q121">
-        <v>2.86</v>
-      </c>
-      <c r="R121">
-        <v>2.23</v>
-      </c>
-      <c r="S121">
-        <v>1.29</v>
-      </c>
-      <c r="T121">
-        <v>3.25</v>
-      </c>
-      <c r="U121">
-        <v>2.38</v>
-      </c>
-      <c r="V121">
-        <v>1.44</v>
-      </c>
-      <c r="W121">
-        <v>1.09</v>
-      </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
-      <c r="Y121">
-        <v>1.18</v>
-      </c>
-      <c r="Z121">
-        <v>3.92</v>
-      </c>
-      <c r="AA121">
-        <v>1.66</v>
-      </c>
-      <c r="AB121">
-        <v>2.15</v>
-      </c>
-      <c r="AC121">
-        <v>2.56</v>
-      </c>
-      <c r="AD121">
-        <v>1.4</v>
-      </c>
-      <c r="AE121">
-        <v>1.13</v>
-      </c>
-      <c r="AF121">
-        <v>1.58</v>
-      </c>
-      <c r="AG121">
-        <v>2.2</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.4</v>
-      </c>
-      <c r="AK121">
-        <v>1.47</v>
-      </c>
-      <c r="AL121">
-        <v>0</v>
-      </c>
-      <c r="AM121">
-        <v>-1</v>
-      </c>
-      <c r="AN121">
-        <v>-1</v>
-      </c>
-      <c r="AO121">
-        <v>-1</v>
-      </c>
-      <c r="AP121">
-        <v>-1</v>
-      </c>
-      <c r="AQ121">
-        <v>0</v>
-      </c>
-      <c r="AR121">
-        <v>0</v>
-      </c>
-      <c r="AS121">
-        <v>0</v>
-      </c>
-      <c r="AT121">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-07-25 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>2.12</v>
-      </c>
-      <c r="O122">
-        <v>4.01</v>
-      </c>
-      <c r="P122">
-        <v>3.23</v>
-      </c>
-      <c r="Q122">
-        <v>2.5</v>
-      </c>
-      <c r="R122">
-        <v>2.45</v>
-      </c>
-      <c r="S122">
-        <v>1.2</v>
-      </c>
-      <c r="T122">
-        <v>4.33</v>
-      </c>
-      <c r="U122">
-        <v>1.95</v>
-      </c>
-      <c r="V122">
-        <v>1.77</v>
-      </c>
-      <c r="W122">
-        <v>1.17</v>
-      </c>
-      <c r="X122">
-        <v>0</v>
-      </c>
-      <c r="Y122">
-        <v>1.06</v>
-      </c>
-      <c r="Z122">
-        <v>7</v>
-      </c>
-      <c r="AA122">
-        <v>1.36</v>
-      </c>
-      <c r="AB122">
-        <v>2.88</v>
-      </c>
-      <c r="AC122">
-        <v>1.98</v>
-      </c>
-      <c r="AD122">
-        <v>1.72</v>
-      </c>
-      <c r="AE122">
-        <v>1.29</v>
-      </c>
-      <c r="AF122">
-        <v>1.36</v>
-      </c>
-      <c r="AG122">
-        <v>2.9</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.22</v>
-      </c>
-      <c r="AK122">
-        <v>1.7</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>2026-07-25 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Monterey Bay</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>1.99</v>
-      </c>
-      <c r="O123">
-        <v>3.45</v>
-      </c>
-      <c r="P123">
-        <v>3.2</v>
-      </c>
-      <c r="Q123">
-        <v>2.75</v>
-      </c>
-      <c r="R123">
-        <v>2.16</v>
-      </c>
-      <c r="S123">
-        <v>1.34</v>
-      </c>
-      <c r="T123">
-        <v>2.7</v>
-      </c>
-      <c r="U123">
-        <v>2.89</v>
-      </c>
-      <c r="V123">
-        <v>1.36</v>
-      </c>
-      <c r="W123">
-        <v>1.04</v>
-      </c>
-      <c r="X123">
-        <v>1</v>
-      </c>
-      <c r="Y123">
-        <v>1.28</v>
-      </c>
-      <c r="Z123">
-        <v>3.15</v>
-      </c>
-      <c r="AA123">
-        <v>1.79</v>
-      </c>
-      <c r="AB123">
-        <v>1.88</v>
-      </c>
-      <c r="AC123">
-        <v>3.2</v>
-      </c>
-      <c r="AD123">
-        <v>1.26</v>
-      </c>
-      <c r="AE123">
-        <v>1.05</v>
-      </c>
-      <c r="AF123">
-        <v>1.72</v>
-      </c>
-      <c r="AG123">
-        <v>1.97</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.24</v>
-      </c>
-      <c r="AK123">
-        <v>1.5</v>
-      </c>
-      <c r="AL123">
-        <v>0</v>
-      </c>
-      <c r="AM123">
-        <v>-1</v>
-      </c>
-      <c r="AN123">
-        <v>-1</v>
-      </c>
-      <c r="AO123">
-        <v>-1</v>
-      </c>
-      <c r="AP123">
-        <v>-1</v>
-      </c>
-      <c r="AQ123">
-        <v>0</v>
-      </c>
-      <c r="AR123">
-        <v>0</v>
-      </c>
-      <c r="AS123">
-        <v>0</v>
-      </c>
-      <c r="AT123">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-07-25 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>2.35</v>
-      </c>
-      <c r="O124">
-        <v>3.15</v>
-      </c>
-      <c r="P124">
-        <v>2.72</v>
-      </c>
-      <c r="Q124">
-        <v>3</v>
-      </c>
-      <c r="R124">
-        <v>2.05</v>
-      </c>
-      <c r="S124">
-        <v>1.38</v>
-      </c>
-      <c r="T124">
-        <v>2.7</v>
-      </c>
-      <c r="U124">
-        <v>2.82</v>
-      </c>
-      <c r="V124">
-        <v>1.35</v>
-      </c>
-      <c r="W124">
-        <v>1.03</v>
-      </c>
-      <c r="X124">
-        <v>1.01</v>
-      </c>
-      <c r="Y124">
-        <v>1.28</v>
-      </c>
-      <c r="Z124">
-        <v>3.05</v>
-      </c>
-      <c r="AA124">
-        <v>1.99</v>
-      </c>
-      <c r="AB124">
-        <v>1.72</v>
-      </c>
-      <c r="AC124">
-        <v>3.42</v>
-      </c>
-      <c r="AD124">
-        <v>1.23</v>
-      </c>
-      <c r="AE124">
-        <v>1.04</v>
-      </c>
-      <c r="AF124">
-        <v>1.76</v>
-      </c>
-      <c r="AG124">
-        <v>1.94</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.26</v>
-      </c>
-      <c r="AK124">
-        <v>1.46</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-07-25 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>2.06</v>
-      </c>
-      <c r="O125">
-        <v>3.4</v>
-      </c>
-      <c r="P125">
-        <v>3.1</v>
-      </c>
-      <c r="Q125">
-        <v>2.68</v>
-      </c>
-      <c r="R125">
-        <v>2.25</v>
-      </c>
-      <c r="S125">
-        <v>1.33</v>
-      </c>
-      <c r="T125">
-        <v>2.91</v>
-      </c>
-      <c r="U125">
-        <v>2.59</v>
-      </c>
-      <c r="V125">
-        <v>1.41</v>
-      </c>
-      <c r="W125">
-        <v>1.06</v>
-      </c>
-      <c r="X125">
-        <v>1.01</v>
-      </c>
-      <c r="Y125">
-        <v>1.21</v>
-      </c>
-      <c r="Z125">
-        <v>3.48</v>
-      </c>
-      <c r="AA125">
-        <v>1.76</v>
-      </c>
-      <c r="AB125">
-        <v>1.92</v>
-      </c>
-      <c r="AC125">
-        <v>2.75</v>
-      </c>
-      <c r="AD125">
-        <v>1.34</v>
-      </c>
-      <c r="AE125">
-        <v>1.08</v>
-      </c>
-      <c r="AF125">
-        <v>1.66</v>
-      </c>
-      <c r="AG125">
-        <v>2.18</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.23</v>
-      </c>
-      <c r="AK125">
-        <v>1.47</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-07-25 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>1.21</v>
-      </c>
-      <c r="O126">
-        <v>7.95</v>
-      </c>
-      <c r="P126">
-        <v>12.7</v>
-      </c>
-      <c r="Q126">
-        <v>1.5</v>
-      </c>
-      <c r="R126">
-        <v>3.13</v>
-      </c>
-      <c r="S126">
-        <v>1.15</v>
-      </c>
-      <c r="T126">
-        <v>5</v>
-      </c>
-      <c r="U126">
-        <v>1.79</v>
-      </c>
-      <c r="V126">
-        <v>1.88</v>
-      </c>
-      <c r="W126">
-        <v>1.25</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>1.05</v>
-      </c>
-      <c r="Z126">
-        <v>8</v>
-      </c>
-      <c r="AA126">
-        <v>1.3</v>
-      </c>
-      <c r="AB126">
-        <v>3.35</v>
-      </c>
-      <c r="AC126">
-        <v>1.71</v>
-      </c>
-      <c r="AD126">
-        <v>1.98</v>
-      </c>
-      <c r="AE126">
-        <v>1.44</v>
-      </c>
-      <c r="AF126">
-        <v>1.73</v>
-      </c>
-      <c r="AG126">
-        <v>2.05</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.06</v>
-      </c>
-      <c r="AK126">
-        <v>4.5</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-07-25 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>1.71</v>
-      </c>
-      <c r="O127">
-        <v>4.65</v>
-      </c>
-      <c r="P127">
-        <v>4.33</v>
-      </c>
-      <c r="Q127">
-        <v>2.15</v>
-      </c>
-      <c r="R127">
-        <v>2.45</v>
-      </c>
-      <c r="S127">
-        <v>1.2</v>
-      </c>
-      <c r="T127">
-        <v>4</v>
-      </c>
-      <c r="U127">
-        <v>2.02</v>
-      </c>
-      <c r="V127">
-        <v>1.65</v>
-      </c>
-      <c r="W127">
-        <v>1.14</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>1.11</v>
-      </c>
-      <c r="Z127">
-        <v>6</v>
-      </c>
-      <c r="AA127">
-        <v>1.4</v>
-      </c>
-      <c r="AB127">
-        <v>2.75</v>
-      </c>
-      <c r="AC127">
-        <v>2.05</v>
-      </c>
-      <c r="AD127">
-        <v>1.66</v>
-      </c>
-      <c r="AE127">
-        <v>1.29</v>
-      </c>
-      <c r="AF127">
-        <v>1.44</v>
-      </c>
-      <c r="AG127">
-        <v>2.55</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.2</v>
-      </c>
-      <c r="AK127">
-        <v>2.2</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-07-25 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>2.36</v>
-      </c>
-      <c r="O128">
-        <v>4.3</v>
-      </c>
-      <c r="P128">
-        <v>2.67</v>
-      </c>
-      <c r="Q128">
-        <v>2.8</v>
-      </c>
-      <c r="R128">
-        <v>2.4</v>
-      </c>
-      <c r="S128">
-        <v>1.22</v>
-      </c>
-      <c r="T128">
-        <v>3.85</v>
-      </c>
-      <c r="U128">
-        <v>2</v>
-      </c>
-      <c r="V128">
-        <v>1.68</v>
-      </c>
-      <c r="W128">
-        <v>1.17</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>1.11</v>
-      </c>
-      <c r="Z128">
-        <v>6</v>
-      </c>
-      <c r="AA128">
-        <v>1.38</v>
-      </c>
-      <c r="AB128">
-        <v>2.64</v>
-      </c>
-      <c r="AC128">
-        <v>2.05</v>
-      </c>
-      <c r="AD128">
-        <v>1.66</v>
-      </c>
-      <c r="AE128">
-        <v>1.25</v>
-      </c>
-      <c r="AF128">
-        <v>1.36</v>
-      </c>
-      <c r="AG128">
-        <v>2.88</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.25</v>
-      </c>
-      <c r="AK128">
-        <v>1.57</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-07-25 23:30:00</t>
         </is>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G59">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="O85">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="P85">
-        <v>6.63</v>
+        <v>7</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14342,7 +14342,7 @@
         <v>1.95</v>
       </c>
       <c r="S86">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T86">
         <v>2.44</v>
@@ -14351,13 +14351,13 @@
         <v>3.4</v>
       </c>
       <c r="V86">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X86">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
         <v>1.43</v>
@@ -14366,16 +14366,16 @@
         <v>2.61</v>
       </c>
       <c r="AA86">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AB86">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC86">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE86">
         <v>1.03</v>
@@ -14384,7 +14384,7 @@
         <v>2.01</v>
       </c>
       <c r="AG86">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.34</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.41</v>
+        <v>1.71</v>
       </c>
       <c r="O95">
-        <v>3.06</v>
+        <v>3.86</v>
       </c>
       <c r="P95">
-        <v>2.71</v>
+        <v>3.92</v>
       </c>
       <c r="Q95">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="R95">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="S95">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>3.12</v>
+        <v>2.52</v>
       </c>
       <c r="V95">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
+        <v>1.09</v>
+      </c>
+      <c r="X95">
         <v>1.02</v>
       </c>
-      <c r="X95">
-        <v>1.04</v>
-      </c>
       <c r="Y95">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>2.66</v>
+        <v>4.15</v>
       </c>
       <c r="AA95">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="AB95">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC95">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD95">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE95">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AG95">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK95">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.71</v>
+        <v>2.41</v>
       </c>
       <c r="O96">
-        <v>3.86</v>
+        <v>3.06</v>
       </c>
       <c r="P96">
-        <v>3.92</v>
+        <v>2.71</v>
       </c>
       <c r="Q96">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="R96">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="S96">
+        <v>1.47</v>
+      </c>
+      <c r="T96">
+        <v>2.6</v>
+      </c>
+      <c r="U96">
+        <v>3.12</v>
+      </c>
+      <c r="V96">
         <v>1.29</v>
       </c>
-      <c r="T96">
-        <v>3.25</v>
-      </c>
-      <c r="U96">
-        <v>2.52</v>
-      </c>
-      <c r="V96">
-        <v>1.53</v>
-      </c>
       <c r="W96">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
+        <v>1.04</v>
+      </c>
+      <c r="Y96">
+        <v>1.37</v>
+      </c>
+      <c r="Z96">
+        <v>2.66</v>
+      </c>
+      <c r="AA96">
+        <v>2.29</v>
+      </c>
+      <c r="AB96">
+        <v>1.6</v>
+      </c>
+      <c r="AC96">
+        <v>4.2</v>
+      </c>
+      <c r="AD96">
+        <v>1.2</v>
+      </c>
+      <c r="AE96">
         <v>1.02</v>
       </c>
-      <c r="Y96">
-        <v>1.16</v>
-      </c>
-      <c r="Z96">
-        <v>4.15</v>
-      </c>
-      <c r="AA96">
-        <v>1.65</v>
-      </c>
-      <c r="AB96">
-        <v>2.15</v>
-      </c>
-      <c r="AC96">
-        <v>2.52</v>
-      </c>
-      <c r="AD96">
-        <v>1.41</v>
-      </c>
-      <c r="AE96">
-        <v>1.13</v>
-      </c>
       <c r="AF96">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AG96">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16292,40 +16292,40 @@
         <v>4.28</v>
       </c>
       <c r="Q98">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S98">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U98">
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z98">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA98">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
         <v>3.44</v>
@@ -16334,10 +16334,10 @@
         <v>1.29</v>
       </c>
       <c r="AE98">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF98">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG98">
         <v>1.9</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="O102">
         <v>3.6</v>
       </c>
       <c r="P102">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q102">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R102">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S102">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U102">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V102">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W102">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z102">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA102">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB102">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC102">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AD102">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE102">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG102">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="O103">
+        <v>3.6</v>
+      </c>
+      <c r="P103">
+        <v>2.16</v>
+      </c>
+      <c r="Q103">
         <v>3.5</v>
       </c>
-      <c r="P103">
-        <v>2.8</v>
-      </c>
-      <c r="Q103">
-        <v>2.84</v>
-      </c>
       <c r="R103">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S103">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U103">
+        <v>2.14</v>
+      </c>
+      <c r="V103">
+        <v>1.6</v>
+      </c>
+      <c r="W103">
+        <v>1.15</v>
+      </c>
+      <c r="X103">
+        <v>1.01</v>
+      </c>
+      <c r="Y103">
+        <v>1.11</v>
+      </c>
+      <c r="Z103">
+        <v>5.25</v>
+      </c>
+      <c r="AA103">
+        <v>1.51</v>
+      </c>
+      <c r="AB103">
+        <v>2.33</v>
+      </c>
+      <c r="AC103">
         <v>2.25</v>
       </c>
-      <c r="V103">
-        <v>1.57</v>
-      </c>
-      <c r="W103">
-        <v>1.12</v>
-      </c>
-      <c r="X103">
-        <v>1.03</v>
-      </c>
-      <c r="Y103">
-        <v>1.15</v>
-      </c>
-      <c r="Z103">
-        <v>4.3</v>
-      </c>
-      <c r="AA103">
-        <v>1.59</v>
-      </c>
-      <c r="AB103">
-        <v>2.17</v>
-      </c>
-      <c r="AC103">
-        <v>2.44</v>
-      </c>
       <c r="AD103">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE103">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF103">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG103">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.17</v>
+        <v>2.26</v>
       </c>
       <c r="O104">
         <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="Q104">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R104">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
+        <v>1.32</v>
+      </c>
+      <c r="T104">
+        <v>3.1</v>
+      </c>
+      <c r="U104">
+        <v>2.55</v>
+      </c>
+      <c r="V104">
+        <v>1.46</v>
+      </c>
+      <c r="W104">
+        <v>1.1</v>
+      </c>
+      <c r="X104">
+        <v>1.04</v>
+      </c>
+      <c r="Y104">
+        <v>1.17</v>
+      </c>
+      <c r="Z104">
+        <v>4.33</v>
+      </c>
+      <c r="AA104">
+        <v>1.67</v>
+      </c>
+      <c r="AB104">
+        <v>2.2</v>
+      </c>
+      <c r="AC104">
+        <v>2.65</v>
+      </c>
+      <c r="AD104">
+        <v>1.48</v>
+      </c>
+      <c r="AE104">
+        <v>1.13</v>
+      </c>
+      <c r="AF104">
+        <v>1.53</v>
+      </c>
+      <c r="AG104">
+        <v>2.3</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.25</v>
       </c>
-      <c r="T104">
-        <v>3.8</v>
-      </c>
-      <c r="U104">
-        <v>2.14</v>
-      </c>
-      <c r="V104">
-        <v>1.6</v>
-      </c>
-      <c r="W104">
-        <v>1.15</v>
-      </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.11</v>
-      </c>
-      <c r="Z104">
-        <v>5.25</v>
-      </c>
-      <c r="AA104">
-        <v>1.51</v>
-      </c>
-      <c r="AB104">
-        <v>2.33</v>
-      </c>
-      <c r="AC104">
-        <v>2.25</v>
-      </c>
-      <c r="AD104">
-        <v>1.56</v>
-      </c>
-      <c r="AE104">
-        <v>1.2</v>
-      </c>
-      <c r="AF104">
-        <v>1.45</v>
-      </c>
-      <c r="AG104">
-        <v>2.51</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.22</v>
-      </c>
       <c r="AK104">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q105">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="R105">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
+        <v>2.25</v>
+      </c>
+      <c r="V105">
+        <v>1.57</v>
+      </c>
+      <c r="W105">
+        <v>1.12</v>
+      </c>
+      <c r="X105">
+        <v>1.03</v>
+      </c>
+      <c r="Y105">
+        <v>1.15</v>
+      </c>
+      <c r="Z105">
+        <v>4.3</v>
+      </c>
+      <c r="AA105">
+        <v>1.59</v>
+      </c>
+      <c r="AB105">
+        <v>2.17</v>
+      </c>
+      <c r="AC105">
         <v>2.44</v>
       </c>
-      <c r="V105">
-        <v>1.45</v>
-      </c>
-      <c r="W105">
-        <v>1.08</v>
-      </c>
-      <c r="X105">
-        <v>1.01</v>
-      </c>
-      <c r="Y105">
-        <v>1.2</v>
-      </c>
-      <c r="Z105">
-        <v>4.1</v>
-      </c>
-      <c r="AA105">
-        <v>1.72</v>
-      </c>
-      <c r="AB105">
-        <v>2</v>
-      </c>
-      <c r="AC105">
-        <v>2.8</v>
-      </c>
       <c r="AD105">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG105">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.57</v>
+        <v>3.41</v>
       </c>
       <c r="O112">
-        <v>4.2</v>
+        <v>3.93</v>
       </c>
       <c r="P112">
-        <v>5.7</v>
+        <v>2.07</v>
       </c>
       <c r="Q112">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="R112">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U112">
         <v>2.25</v>
       </c>
       <c r="V112">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z112">
         <v>4.8</v>
       </c>
       <c r="AA112">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB112">
+        <v>2.25</v>
+      </c>
+      <c r="AC112">
         <v>2.33</v>
       </c>
-      <c r="AC112">
-        <v>2.37</v>
-      </c>
       <c r="AD112">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE112">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF112">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG112">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>2.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.41</v>
+        <v>1.57</v>
       </c>
       <c r="O113">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="P113">
-        <v>2.07</v>
+        <v>5.7</v>
       </c>
       <c r="Q113">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="R113">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T113">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U113">
         <v>2.25</v>
       </c>
       <c r="V113">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W113">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z113">
         <v>4.8</v>
       </c>
       <c r="AA113">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB113">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC113">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AD113">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE113">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF113">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG113">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK113">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL113">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O14">
-        <v>5.24</v>
+        <v>4.65</v>
       </c>
       <c r="P14">
-        <v>8.85</v>
+        <v>6.75</v>
       </c>
       <c r="Q14">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R14">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U14">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
         <v>1.49</v>
@@ -2624,22 +2624,22 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
@@ -2664,7 +2664,7 @@
         <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4070,49 +4070,49 @@
         <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
         <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB23">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC23">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
         <v>1.97</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>3.69</v>
+        <v>3.15</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
         <v>2.77</v>
       </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
         <v>1.92</v>
       </c>
       <c r="AB24">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
         <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
         <v>3.2</v>
@@ -4420,10 +4420,10 @@
         <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB25">
         <v>1.64</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK25">
         <v>1.6</v>
@@ -4873,61 +4873,61 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P28">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
         <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.09</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>3.65</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
         <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AG28">
         <v>2.07</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,34 +5036,34 @@
         </is>
       </c>
       <c r="N29">
-        <v>6.98</v>
+        <v>8.1</v>
       </c>
       <c r="O29">
-        <v>5.24</v>
+        <v>4.75</v>
       </c>
       <c r="P29">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="Q29">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="R29">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T29">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="U29">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,44 +5072,44 @@
         <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AC29">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AD29">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE29">
+        <v>1.21</v>
+      </c>
+      <c r="AF29">
+        <v>1.85</v>
+      </c>
+      <c r="AG29">
+        <v>1.87</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.18</v>
       </c>
-      <c r="AF29">
-        <v>1.86</v>
-      </c>
-      <c r="AG29">
-        <v>1.86</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.13</v>
-      </c>
       <c r="AK29">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="O30">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P31">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q31">
         <v>4.62</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -5392,25 +5392,25 @@
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB31">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
         <v>1.1</v>
@@ -5419,7 +5419,7 @@
         <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="O32">
+        <v>3.35</v>
+      </c>
+      <c r="P32">
+        <v>2.17</v>
+      </c>
+      <c r="Q32">
         <v>3.4</v>
       </c>
-      <c r="P32">
-        <v>2.22</v>
-      </c>
-      <c r="Q32">
-        <v>3.1</v>
-      </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V32">
         <v>1.55</v>
@@ -5561,13 +5561,13 @@
         <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA32">
         <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
         <v>2.35</v>
@@ -5576,13 +5576,13 @@
         <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG32">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,52 +5688,52 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="O33">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P33">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="Q33">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="R33">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U33">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
         <v>1.76</v>
       </c>
       <c r="AC33">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD33">
         <v>1.24</v>
@@ -5742,10 +5742,10 @@
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>3.86</v>
       </c>
       <c r="Q36">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="R36">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="U36">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA36">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
         <v>1.7</v>
       </c>
       <c r="AC36">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD36">
         <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="O39">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S39">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T39">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U39">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
         <v>1.03</v>
@@ -6699,31 +6699,31 @@
         <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z39">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA39">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.14</v>
+        <v>3.59</v>
       </c>
       <c r="AD39">
         <v>1.27</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK39">
         <v>1.54</v>
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R40">
         <v>2.35</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
         <v>3.24</v>
       </c>
       <c r="U40">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,28 +6865,28 @@
         <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
         <v>1.72</v>
       </c>
       <c r="AG40">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
         <v>2.43</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="O42">
         <v>3.12</v>
       </c>
       <c r="P42">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="Q42">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="R42">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7194,10 +7194,10 @@
         <v>3.75</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
         <v>2.8</v>
@@ -7206,13 +7206,13 @@
         <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.34</v>
       </c>
       <c r="AK42">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="O43">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA43">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7674,22 +7674,22 @@
         <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y45">
         <v>1.52</v>
       </c>
       <c r="Z45">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AA45">
         <v>2.64</v>
       </c>
       <c r="AB45">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AC45">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AD45">
         <v>1.14</v>
@@ -7701,7 +7701,7 @@
         <v>2.11</v>
       </c>
       <c r="AG45">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="O48">
-        <v>3.84</v>
+        <v>3.61</v>
       </c>
       <c r="P48">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U48">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W48">
         <v>1.12</v>
@@ -8166,31 +8166,31 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
         <v>4.3</v>
       </c>
       <c r="AA48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC48">
         <v>2.38</v>
       </c>
       <c r="AD48">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="O49">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
       </c>
       <c r="R49">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="S49">
         <v>1.17</v>
@@ -8317,10 +8317,10 @@
         <v>4.5</v>
       </c>
       <c r="U49">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V49">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W49">
         <v>1.17</v>
@@ -8329,31 +8329,31 @@
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA49">
         <v>1.47</v>
       </c>
       <c r="AB49">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AC49">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD49">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE49">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF49">
         <v>1.38</v>
       </c>
       <c r="AG49">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
         <v>1.53</v>
@@ -8468,55 +8468,55 @@
         <v>2.07</v>
       </c>
       <c r="Q50">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="R50">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
         <v>3.2</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB50">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD50">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
         <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,52 +8785,52 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="O52">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P52">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q52">
-        <v>3.7</v>
+        <v>4.02</v>
       </c>
       <c r="R52">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U52">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W52">
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC52">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AD52">
         <v>1.28</v>
@@ -8839,26 +8839,26 @@
         <v>1.06</v>
       </c>
       <c r="AF52">
+        <v>1.7</v>
+      </c>
+      <c r="AG52">
+        <v>2.05</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.67</v>
       </c>
-      <c r="AG52">
-        <v>2.04</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.25</v>
-      </c>
       <c r="AK52">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q53">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
         <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB53">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AD53">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,28 +9111,28 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="O54">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="P54">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="Q54">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="R54">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="V54">
         <v>1.4</v>
@@ -9141,7 +9141,7 @@
         <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.25</v>
@@ -9150,25 +9150,25 @@
         <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC54">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG54">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK54">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>1.99</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P61">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O62">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="P62">
-        <v>9.550000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q62">
         <v>1.68</v>
       </c>
       <c r="R62">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="S62">
         <v>1.21</v>
@@ -10451,7 +10451,7 @@
         <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>5.36</v>
+        <v>5.65</v>
       </c>
       <c r="AA62">
         <v>1.42</v>
@@ -10460,19 +10460,19 @@
         <v>2.66</v>
       </c>
       <c r="AC62">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AD62">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF62">
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
         <v>3.62</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O66">
         <v>3.08</v>
       </c>
       <c r="P66">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="Q66">
         <v>2.43</v>
@@ -11082,22 +11082,22 @@
         <v>1.89</v>
       </c>
       <c r="S66">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T66">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U66">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V66">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W66">
         <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y66">
         <v>1.65</v>
@@ -11106,13 +11106,13 @@
         <v>2.11</v>
       </c>
       <c r="AA66">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="AB66">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC66">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="AD66">
         <v>1.07</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="O67">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="P67">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="Q67">
         <v>2.71</v>
@@ -11245,10 +11245,10 @@
         <v>1.74</v>
       </c>
       <c r="S67">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="T67">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U67">
         <v>4.2</v>
@@ -11263,10 +11263,10 @@
         <v>1.1</v>
       </c>
       <c r="Y67">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Z67">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AA67">
         <v>3.04</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P68">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -11408,49 +11408,49 @@
         <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z68">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA68">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AC68">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD68">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O71">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P71">
-        <v>6.34</v>
+        <v>5.25</v>
       </c>
       <c r="Q71">
         <v>1.96</v>
@@ -11897,13 +11897,13 @@
         <v>2.35</v>
       </c>
       <c r="S71">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="U71">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="V71">
         <v>1.5</v>
@@ -11921,13 +11921,13 @@
         <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB71">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC71">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD71">
         <v>1.38</v>
@@ -11936,10 +11936,10 @@
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P72">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Q72">
-        <v>6</v>
+        <v>6.23</v>
       </c>
       <c r="R72">
         <v>2.27</v>
       </c>
       <c r="S72">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="V72">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W72">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA72">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB72">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC72">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE72">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AK72">
         <v>1.09</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="O73">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
-        <v>2.43</v>
+        <v>2.78</v>
       </c>
       <c r="Q73">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="R73">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="S73">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T73">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="U73">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V73">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
         <v>1.07</v>
       </c>
       <c r="Z73">
-        <v>6.21</v>
+        <v>5.8</v>
       </c>
       <c r="AA73">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB73">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="AC73">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AD73">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AE73">
         <v>1.3</v>
       </c>
       <c r="AF73">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG73">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13195,7 +13195,7 @@
         <v>3.75</v>
       </c>
       <c r="Q79">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R79">
         <v>1.83</v>
@@ -13207,22 +13207,22 @@
         <v>2.04</v>
       </c>
       <c r="U79">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="V79">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W79">
         <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y79">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Z79">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AA79">
         <v>3.08</v>
@@ -13231,7 +13231,7 @@
         <v>1.32</v>
       </c>
       <c r="AC79">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="AD79">
         <v>1.04</v>
@@ -13240,10 +13240,10 @@
         <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG79">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q104">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="R104">
         <v>2.3</v>
       </c>
       <c r="S104">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U104">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="V104">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
+        <v>1.15</v>
+      </c>
+      <c r="Z104">
+        <v>4.3</v>
+      </c>
+      <c r="AA104">
+        <v>1.59</v>
+      </c>
+      <c r="AB104">
+        <v>2.17</v>
+      </c>
+      <c r="AC104">
+        <v>2.44</v>
+      </c>
+      <c r="AD104">
+        <v>1.49</v>
+      </c>
+      <c r="AE104">
         <v>1.17</v>
       </c>
-      <c r="Z104">
-        <v>4.33</v>
-      </c>
-      <c r="AA104">
-        <v>1.67</v>
-      </c>
-      <c r="AB104">
-        <v>2.2</v>
-      </c>
-      <c r="AC104">
-        <v>2.65</v>
-      </c>
-      <c r="AD104">
-        <v>1.48</v>
-      </c>
-      <c r="AE104">
-        <v>1.13</v>
-      </c>
       <c r="AF104">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG104">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q105">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="R105">
         <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U105">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
+        <v>1.46</v>
+      </c>
+      <c r="W105">
+        <v>1.1</v>
+      </c>
+      <c r="X105">
+        <v>1.04</v>
+      </c>
+      <c r="Y105">
+        <v>1.17</v>
+      </c>
+      <c r="Z105">
+        <v>4.33</v>
+      </c>
+      <c r="AA105">
+        <v>1.67</v>
+      </c>
+      <c r="AB105">
+        <v>2.2</v>
+      </c>
+      <c r="AC105">
+        <v>2.65</v>
+      </c>
+      <c r="AD105">
+        <v>1.48</v>
+      </c>
+      <c r="AE105">
+        <v>1.13</v>
+      </c>
+      <c r="AF105">
+        <v>1.53</v>
+      </c>
+      <c r="AG105">
+        <v>2.3</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
+        <v>1.25</v>
+      </c>
+      <c r="AK105">
         <v>1.57</v>
-      </c>
-      <c r="W105">
-        <v>1.12</v>
-      </c>
-      <c r="X105">
-        <v>1.03</v>
-      </c>
-      <c r="Y105">
-        <v>1.15</v>
-      </c>
-      <c r="Z105">
-        <v>4.3</v>
-      </c>
-      <c r="AA105">
-        <v>1.59</v>
-      </c>
-      <c r="AB105">
-        <v>2.17</v>
-      </c>
-      <c r="AC105">
-        <v>2.44</v>
-      </c>
-      <c r="AD105">
-        <v>1.49</v>
-      </c>
-      <c r="AE105">
-        <v>1.17</v>
-      </c>
-      <c r="AF105">
-        <v>1.5</v>
-      </c>
-      <c r="AG105">
-        <v>2.38</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.22</v>
-      </c>
-      <c r="AK105">
-        <v>1.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,65 +20032,65 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="O121">
-        <v>3.84</v>
+        <v>6.5</v>
       </c>
       <c r="P121">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q121">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="R121">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="S121">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T121">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="U121">
+        <v>1.75</v>
+      </c>
+      <c r="V121">
+        <v>1.95</v>
+      </c>
+      <c r="W121">
+        <v>1.25</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>1.08</v>
+      </c>
+      <c r="Z121">
+        <v>7.5</v>
+      </c>
+      <c r="AA121">
+        <v>1.25</v>
+      </c>
+      <c r="AB121">
+        <v>3.8</v>
+      </c>
+      <c r="AC121">
+        <v>1.67</v>
+      </c>
+      <c r="AD121">
+        <v>2.15</v>
+      </c>
+      <c r="AE121">
+        <v>1.48</v>
+      </c>
+      <c r="AF121">
+        <v>1.77</v>
+      </c>
+      <c r="AG121">
         <v>2.1</v>
       </c>
-      <c r="V121">
-        <v>1.67</v>
-      </c>
-      <c r="W121">
-        <v>1.18</v>
-      </c>
-      <c r="X121">
-        <v>0</v>
-      </c>
-      <c r="Y121">
-        <v>1.13</v>
-      </c>
-      <c r="Z121">
-        <v>5.75</v>
-      </c>
-      <c r="AA121">
-        <v>1.44</v>
-      </c>
-      <c r="AB121">
-        <v>2.75</v>
-      </c>
-      <c r="AC121">
-        <v>2.05</v>
-      </c>
-      <c r="AD121">
-        <v>1.73</v>
-      </c>
-      <c r="AE121">
-        <v>1.25</v>
-      </c>
-      <c r="AF121">
-        <v>1.4</v>
-      </c>
-      <c r="AG121">
-        <v>2.8</v>
-      </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AK121">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="O122">
-        <v>6.5</v>
+        <v>3.84</v>
       </c>
       <c r="P122">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q122">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="R122">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="S122">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T122">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="U122">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="V122">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="W122">
+        <v>1.18</v>
+      </c>
+      <c r="X122">
+        <v>0</v>
+      </c>
+      <c r="Y122">
+        <v>1.13</v>
+      </c>
+      <c r="Z122">
+        <v>5.75</v>
+      </c>
+      <c r="AA122">
+        <v>1.44</v>
+      </c>
+      <c r="AB122">
+        <v>2.75</v>
+      </c>
+      <c r="AC122">
+        <v>2.05</v>
+      </c>
+      <c r="AD122">
+        <v>1.73</v>
+      </c>
+      <c r="AE122">
         <v>1.25</v>
       </c>
-      <c r="X122">
-        <v>0</v>
-      </c>
-      <c r="Y122">
-        <v>1.08</v>
-      </c>
-      <c r="Z122">
-        <v>7.5</v>
-      </c>
-      <c r="AA122">
-        <v>1.25</v>
-      </c>
-      <c r="AB122">
-        <v>3.8</v>
-      </c>
-      <c r="AC122">
-        <v>1.67</v>
-      </c>
-      <c r="AD122">
-        <v>2.15</v>
-      </c>
-      <c r="AE122">
-        <v>1.48</v>
-      </c>
       <c r="AF122">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AG122">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AK122">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -644,16 +644,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>5.98</v>
+        <v>5.4</v>
       </c>
       <c r="R2">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U2">
         <v>2.36</v>
@@ -665,34 +665,34 @@
         <v>1.09</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB2">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC2">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE2">
         <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P3">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>4.25</v>
       </c>
       <c r="P4">
-        <v>5.6</v>
+        <v>5.54</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1133,25 +1133,25 @@
         <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,44 +1160,44 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB5">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
+        <v>1.38</v>
+      </c>
+      <c r="AE5">
+        <v>1.16</v>
+      </c>
+      <c r="AF5">
+        <v>1.53</v>
+      </c>
+      <c r="AG5">
+        <v>2.29</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.49</v>
+      </c>
+      <c r="AK5">
         <v>1.37</v>
-      </c>
-      <c r="AE5">
-        <v>1.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.55</v>
-      </c>
-      <c r="AG5">
-        <v>2.24</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.23</v>
-      </c>
-      <c r="AK5">
-        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1459,19 +1459,19 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V7">
         <v>1.37</v>
@@ -1480,25 +1480,25 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1507,7 +1507,7 @@
         <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.25</v>
+      </c>
+      <c r="Z8">
+        <v>3.3</v>
+      </c>
+      <c r="AA8">
+        <v>1.96</v>
+      </c>
+      <c r="AB8">
+        <v>1.88</v>
+      </c>
+      <c r="AC8">
+        <v>3.25</v>
+      </c>
+      <c r="AD8">
+        <v>1.29</v>
+      </c>
+      <c r="AE8">
+        <v>1.08</v>
+      </c>
+      <c r="AF8">
+        <v>1.68</v>
+      </c>
+      <c r="AG8">
+        <v>2.06</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.27</v>
       </c>
-      <c r="Z8">
-        <v>3.62</v>
-      </c>
-      <c r="AA8">
-        <v>1.9</v>
-      </c>
-      <c r="AB8">
-        <v>1.9</v>
-      </c>
-      <c r="AC8">
-        <v>3.17</v>
-      </c>
-      <c r="AD8">
+      <c r="AK8">
         <v>1.34</v>
-      </c>
-      <c r="AE8">
-        <v>1.12</v>
-      </c>
-      <c r="AF8">
-        <v>1.71</v>
-      </c>
-      <c r="AG8">
-        <v>1.9</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.31</v>
-      </c>
-      <c r="AK8">
-        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
+        <v>2.92</v>
+      </c>
+      <c r="O9">
         <v>3.05</v>
       </c>
-      <c r="O9">
-        <v>2.95</v>
-      </c>
       <c r="P9">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>3.89</v>
+        <v>3.39</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="S9">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V9">
         <v>1.28</v>
@@ -1806,34 +1806,34 @@
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AA9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC9">
-        <v>4.41</v>
+        <v>4.2</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="O10">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3.51</v>
+        <v>2.88</v>
       </c>
       <c r="Q10">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="R10">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
         <v>1.65</v>
@@ -1981,22 +1981,22 @@
         <v>1.46</v>
       </c>
       <c r="AB10">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC10">
         <v>2.17</v>
       </c>
       <c r="AD10">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
         <v>1.44</v>
       </c>
       <c r="AG10">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="O11">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
         <v>2.1</v>
@@ -2120,10 +2120,10 @@
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="V11">
         <v>1.36</v>
@@ -2135,22 +2135,22 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
@@ -2159,7 +2159,7 @@
         <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,61 +2265,61 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="O12">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
         <v>2.86</v>
       </c>
-      <c r="Q12">
-        <v>2.88</v>
-      </c>
       <c r="R12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA12">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
         <v>1.9</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="O13">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="P13">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R13">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S13">
         <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
         <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
         <v>1.04</v>
@@ -2464,16 +2464,16 @@
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB13">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD13">
         <v>1.31</v>
@@ -2482,7 +2482,7 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG13">
         <v>2.1</v>
@@ -2501,7 +2501,7 @@
         <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="U20">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.57</v>
+        <v>5.48</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AD20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG20">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="P21">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="Q21">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S21">
         <v>1.21</v>
@@ -3753,10 +3753,10 @@
         <v>3.68</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W21">
         <v>1.17</v>
@@ -3765,47 +3765,47 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>8.050000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AA21">
+        <v>1.44</v>
+      </c>
+      <c r="AB21">
+        <v>2.7</v>
+      </c>
+      <c r="AC21">
+        <v>2.09</v>
+      </c>
+      <c r="AD21">
+        <v>1.76</v>
+      </c>
+      <c r="AE21">
+        <v>1.29</v>
+      </c>
+      <c r="AF21">
+        <v>1.36</v>
+      </c>
+      <c r="AG21">
+        <v>2.89</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.45</v>
       </c>
-      <c r="AB21">
-        <v>2.83</v>
-      </c>
-      <c r="AC21">
-        <v>1.94</v>
-      </c>
-      <c r="AD21">
-        <v>1.75</v>
-      </c>
-      <c r="AE21">
-        <v>1.31</v>
-      </c>
-      <c r="AF21">
-        <v>1.37</v>
-      </c>
-      <c r="AG21">
-        <v>2.86</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.26</v>
-      </c>
       <c r="AK21">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="Q22">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R22">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
         <v>2.81</v>
       </c>
       <c r="U22">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22">
         <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA22">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AB22">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="AD22">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R26">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
         <v>1.25</v>
@@ -4568,13 +4568,13 @@
         <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4589,19 +4589,19 @@
         <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="AC26">
         <v>2.42</v>
       </c>
       <c r="AD26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
         <v>2.5</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.84</v>
+        <v>4.1</v>
       </c>
       <c r="O27">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
         <v>1.31</v>
       </c>
       <c r="T27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
         <v>2.4</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z27">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD27">
         <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG27">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
         <v>2.18</v>
@@ -5878,7 +5878,7 @@
         <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5893,22 +5893,22 @@
         <v>1.74</v>
       </c>
       <c r="AB34">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC34">
         <v>2.64</v>
       </c>
       <c r="AD34">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>1.36</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -6035,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
         <v>0</v>
@@ -6047,31 +6047,31 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA41">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AB41">
+        <v>2.1</v>
+      </c>
+      <c r="AC41">
+        <v>2.56</v>
+      </c>
+      <c r="AD41">
+        <v>1.4</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
         <v>1.72</v>
       </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="O44">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>2.95</v>
+        <v>2.71</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S44">
         <v>1.35</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V44">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AA44">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB44">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC44">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD44">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O47">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="P47">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="Q47">
         <v>2.36</v>
@@ -7988,46 +7988,46 @@
         <v>1.24</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U47">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V47">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>5.26</v>
+        <v>4.8</v>
       </c>
       <c r="AA47">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AE47">
         <v>1.19</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG47">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="O48">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S48">
+        <v>1.17</v>
+      </c>
+      <c r="T48">
+        <v>4.5</v>
+      </c>
+      <c r="U48">
+        <v>2</v>
+      </c>
+      <c r="V48">
+        <v>1.73</v>
+      </c>
+      <c r="W48">
+        <v>1.17</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.14</v>
+      </c>
+      <c r="Z48">
+        <v>5.75</v>
+      </c>
+      <c r="AA48">
+        <v>1.47</v>
+      </c>
+      <c r="AB48">
+        <v>2.6</v>
+      </c>
+      <c r="AC48">
+        <v>2.11</v>
+      </c>
+      <c r="AD48">
+        <v>1.7</v>
+      </c>
+      <c r="AE48">
+        <v>1.24</v>
+      </c>
+      <c r="AF48">
+        <v>1.38</v>
+      </c>
+      <c r="AG48">
+        <v>2.76</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.25</v>
       </c>
-      <c r="T48">
-        <v>3.45</v>
-      </c>
-      <c r="U48">
-        <v>2.3</v>
-      </c>
-      <c r="V48">
-        <v>1.6</v>
-      </c>
-      <c r="W48">
-        <v>1.12</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.15</v>
-      </c>
-      <c r="Z48">
-        <v>4.3</v>
-      </c>
-      <c r="AA48">
-        <v>1.6</v>
-      </c>
-      <c r="AB48">
-        <v>2.29</v>
-      </c>
-      <c r="AC48">
-        <v>2.38</v>
-      </c>
-      <c r="AD48">
-        <v>1.5</v>
-      </c>
-      <c r="AE48">
-        <v>1.16</v>
-      </c>
-      <c r="AF48">
+      <c r="AK48">
         <v>1.53</v>
-      </c>
-      <c r="AG48">
-        <v>2.35</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.2</v>
-      </c>
-      <c r="AK48">
-        <v>1.85</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="U49">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="W49">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z49">
-        <v>5.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA49">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="AD49">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.76</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="O54">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P54">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Q54">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S54">
         <v>1.36</v>
@@ -9132,13 +9132,13 @@
         <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.03</v>
@@ -9150,10 +9150,10 @@
         <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC54">
         <v>3.04</v>
@@ -9165,10 +9165,10 @@
         <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG54">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK54">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="O55">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P55">
-        <v>6.06</v>
+        <v>6.2</v>
       </c>
       <c r="Q55">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="S55">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T55">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V55">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W55">
         <v>1.25</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
         <v>1.02</v>
       </c>
       <c r="Z55">
-        <v>6.75</v>
+        <v>7.8</v>
       </c>
       <c r="AA55">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB55">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC55">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD55">
         <v>2.14</v>
       </c>
       <c r="AE55">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF55">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG55">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK55">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O64">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P64">
         <v>3.47</v>
       </c>
       <c r="Q64">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="R64">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="S64">
+        <v>1.35</v>
+      </c>
+      <c r="T64">
+        <v>2.82</v>
+      </c>
+      <c r="U64">
+        <v>3</v>
+      </c>
+      <c r="V64">
         <v>1.33</v>
       </c>
-      <c r="T64">
-        <v>2.91</v>
-      </c>
-      <c r="U64">
-        <v>2.66</v>
-      </c>
-      <c r="V64">
-        <v>1.39</v>
-      </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z64">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA64">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB64">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC64">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="AD64">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE64">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG64">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O65">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="P65">
         <v>3.47</v>
       </c>
       <c r="Q65">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="R65">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="U65">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB65">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC65">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="AD65">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG65">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O69">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="P69">
-        <v>5.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q69">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="R69">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S69">
         <v>1.17</v>
@@ -11577,10 +11577,10 @@
         <v>4.1</v>
       </c>
       <c r="U69">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="V69">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W69">
         <v>1.17</v>
@@ -11589,10 +11589,10 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA69">
         <v>1.36</v>
@@ -11601,19 +11601,19 @@
         <v>3.1</v>
       </c>
       <c r="AC69">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD69">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AE69">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF69">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
+        <v>2.46</v>
+      </c>
+      <c r="O74">
+        <v>3.28</v>
+      </c>
+      <c r="P74">
         <v>2.45</v>
       </c>
-      <c r="O74">
-        <v>3.32</v>
-      </c>
-      <c r="P74">
-        <v>2.5</v>
-      </c>
       <c r="Q74">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S74">
         <v>1.33</v>
       </c>
       <c r="T74">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V74">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W74">
         <v>1.06</v>
@@ -12410,25 +12410,25 @@
         <v>3.58</v>
       </c>
       <c r="AA74">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB74">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC74">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD74">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF74">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="O75">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="P75">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="Q75">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S75">
         <v>1.37</v>
@@ -12555,7 +12555,7 @@
         <v>2.85</v>
       </c>
       <c r="U75">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
         <v>1.4</v>
@@ -12573,10 +12573,10 @@
         <v>3.77</v>
       </c>
       <c r="AA75">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB75">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC75">
         <v>2.99</v>
@@ -12585,13 +12585,13 @@
         <v>1.3</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
         <v>1.65</v>
       </c>
       <c r="AG75">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12860,46 +12860,46 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O77">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P77">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="Q77">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R77">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T77">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="V77">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
         <v>1.1</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z77">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AA77">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB77">
         <v>2.08</v>
@@ -12917,7 +12917,7 @@
         <v>1.9</v>
       </c>
       <c r="AG77">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK77">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="O85">
         <v>4.5</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB85">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14336,7 +14336,7 @@
         <v>3.98</v>
       </c>
       <c r="Q86">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R86">
         <v>1.95</v>
@@ -14351,40 +14351,40 @@
         <v>3.4</v>
       </c>
       <c r="V86">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W86">
         <v>1.03</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y86">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z86">
         <v>2.61</v>
       </c>
       <c r="AA86">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AB86">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC86">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE86">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF86">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AG86">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14653,40 +14653,40 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O88">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="P88">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q88">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R88">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
         <v>1.3</v>
       </c>
       <c r="T88">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U88">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
         <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z88">
         <v>3.7</v>
@@ -14695,22 +14695,22 @@
         <v>1.7</v>
       </c>
       <c r="AB88">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC88">
         <v>2.69</v>
       </c>
       <c r="AD88">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF88">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG88">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK88">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15142,49 +15142,49 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
         <v>3.6</v>
       </c>
       <c r="P91">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R91">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U91">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V91">
         <v>1.6</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA91">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB91">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC91">
         <v>2.21</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O92">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P92">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.53</v>
+        <v>4.32</v>
       </c>
       <c r="O93">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="P93">
-        <v>4.9</v>
+        <v>1.67</v>
       </c>
       <c r="Q93">
-        <v>2.09</v>
+        <v>4.78</v>
       </c>
       <c r="R93">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="V93">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
+        <v>1.17</v>
+      </c>
+      <c r="Z93">
+        <v>3.96</v>
+      </c>
+      <c r="AA93">
+        <v>1.67</v>
+      </c>
+      <c r="AB93">
+        <v>2.08</v>
+      </c>
+      <c r="AC93">
+        <v>2.35</v>
+      </c>
+      <c r="AD93">
+        <v>1.39</v>
+      </c>
+      <c r="AE93">
+        <v>1.17</v>
+      </c>
+      <c r="AF93">
+        <v>1.65</v>
+      </c>
+      <c r="AG93">
+        <v>2.1</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>1.2</v>
       </c>
-      <c r="Z93">
-        <v>3.68</v>
-      </c>
-      <c r="AA93">
-        <v>1.83</v>
-      </c>
-      <c r="AB93">
-        <v>1.93</v>
-      </c>
-      <c r="AC93">
-        <v>2.74</v>
-      </c>
-      <c r="AD93">
-        <v>1.35</v>
-      </c>
-      <c r="AE93">
-        <v>1.11</v>
-      </c>
-      <c r="AF93">
-        <v>1.76</v>
-      </c>
-      <c r="AG93">
-        <v>1.94</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.17</v>
-      </c>
       <c r="AK93">
-        <v>2.19</v>
+        <v>1.14</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.32</v>
+        <v>1.57</v>
       </c>
       <c r="O94">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P94">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="Q94">
-        <v>4.78</v>
+        <v>2.24</v>
       </c>
       <c r="R94">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S94">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T94">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U94">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="V94">
         <v>1.5</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.16</v>
       </c>
       <c r="Z94">
-        <v>3.94</v>
+        <v>4.09</v>
       </c>
       <c r="AA94">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB94">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC94">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF94">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG94">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK94">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="O95">
-        <v>3.86</v>
+        <v>2.9</v>
       </c>
       <c r="P95">
-        <v>3.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q95">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="R95">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="S95">
+        <v>1.46</v>
+      </c>
+      <c r="T95">
+        <v>2.44</v>
+      </c>
+      <c r="U95">
+        <v>3.1</v>
+      </c>
+      <c r="V95">
         <v>1.29</v>
       </c>
-      <c r="T95">
-        <v>3.25</v>
-      </c>
-      <c r="U95">
-        <v>2.52</v>
-      </c>
-      <c r="V95">
-        <v>1.53</v>
-      </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X95">
+        <v>1.04</v>
+      </c>
+      <c r="Y95">
+        <v>1.4</v>
+      </c>
+      <c r="Z95">
+        <v>2.66</v>
+      </c>
+      <c r="AA95">
+        <v>2.23</v>
+      </c>
+      <c r="AB95">
+        <v>1.58</v>
+      </c>
+      <c r="AC95">
+        <v>3.98</v>
+      </c>
+      <c r="AD95">
+        <v>1.17</v>
+      </c>
+      <c r="AE95">
         <v>1.02</v>
       </c>
-      <c r="Y95">
-        <v>1.16</v>
-      </c>
-      <c r="Z95">
-        <v>4.15</v>
-      </c>
-      <c r="AA95">
-        <v>1.65</v>
-      </c>
-      <c r="AB95">
-        <v>2.15</v>
-      </c>
-      <c r="AC95">
-        <v>2.52</v>
-      </c>
-      <c r="AD95">
-        <v>1.41</v>
-      </c>
-      <c r="AE95">
-        <v>1.13</v>
-      </c>
       <c r="AF95">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AG95">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.41</v>
+        <v>1.45</v>
       </c>
       <c r="O96">
-        <v>3.06</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>2.71</v>
+        <v>4.45</v>
       </c>
       <c r="Q96">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="R96">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S96">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="U96">
-        <v>3.12</v>
+        <v>2.47</v>
       </c>
       <c r="V96">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W96">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z96">
-        <v>2.66</v>
+        <v>3.68</v>
       </c>
       <c r="AA96">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="AB96">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC96">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD96">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE96">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF96">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AG96">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
-        <v>1.35</v>
+        <v>2.19</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="O97">
+        <v>4.1</v>
+      </c>
+      <c r="P97">
         <v>3.9</v>
-      </c>
-      <c r="P97">
-        <v>3.7</v>
       </c>
       <c r="Q97">
         <v>2.2</v>
@@ -16135,16 +16135,16 @@
         <v>2.63</v>
       </c>
       <c r="S97">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T97">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U97">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V97">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W97">
         <v>1.2</v>
@@ -16153,31 +16153,31 @@
         <v>0</v>
       </c>
       <c r="Y97">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
         <v>7</v>
       </c>
       <c r="AA97">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB97">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AC97">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD97">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE97">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF97">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG97">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
         <v>2.05</v>
@@ -16292,10 +16292,10 @@
         <v>4.28</v>
       </c>
       <c r="Q98">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R98">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S98">
         <v>1.4</v>
@@ -16334,13 +16334,13 @@
         <v>1.29</v>
       </c>
       <c r="AE98">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF98">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG98">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16612,10 +16612,10 @@
         <v>1.97</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P100">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="O101">
         <v>3.8</v>
       </c>
       <c r="P101">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16935,31 +16935,31 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P102">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="Q102">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R102">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S102">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U102">
         <v>2.44</v>
       </c>
       <c r="V102">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W102">
         <v>1.08</v>
@@ -16968,22 +16968,22 @@
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z102">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA102">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB102">
         <v>2</v>
       </c>
       <c r="AC102">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD102">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE102">
         <v>1.11</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.17</v>
+        <v>2.25</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="Q103">
+        <v>2.88</v>
+      </c>
+      <c r="R103">
+        <v>2.25</v>
+      </c>
+      <c r="S103">
+        <v>1.29</v>
+      </c>
+      <c r="T103">
         <v>3.5</v>
       </c>
-      <c r="R103">
-        <v>2.38</v>
-      </c>
-      <c r="S103">
-        <v>1.25</v>
-      </c>
-      <c r="T103">
-        <v>3.8</v>
-      </c>
       <c r="U103">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="V103">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W103">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z103">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA103">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC103">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AD103">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE103">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG103">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O104">
+        <v>3.6</v>
+      </c>
+      <c r="P104">
+        <v>2</v>
+      </c>
+      <c r="Q104">
         <v>3.5</v>
-      </c>
-      <c r="P104">
-        <v>2.8</v>
-      </c>
-      <c r="Q104">
-        <v>2.84</v>
       </c>
       <c r="R104">
         <v>2.3</v>
       </c>
       <c r="S104">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T104">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U104">
+        <v>2.15</v>
+      </c>
+      <c r="V104">
+        <v>1.6</v>
+      </c>
+      <c r="W104">
+        <v>1.13</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.11</v>
+      </c>
+      <c r="Z104">
+        <v>5.2</v>
+      </c>
+      <c r="AA104">
+        <v>1.5</v>
+      </c>
+      <c r="AB104">
+        <v>2.4</v>
+      </c>
+      <c r="AC104">
         <v>2.25</v>
       </c>
-      <c r="V104">
+      <c r="AD104">
         <v>1.57</v>
       </c>
-      <c r="W104">
-        <v>1.12</v>
-      </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
-      <c r="Y104">
-        <v>1.15</v>
-      </c>
-      <c r="Z104">
-        <v>4.3</v>
-      </c>
-      <c r="AA104">
-        <v>1.59</v>
-      </c>
-      <c r="AB104">
-        <v>2.17</v>
-      </c>
-      <c r="AC104">
-        <v>2.44</v>
-      </c>
-      <c r="AD104">
-        <v>1.49</v>
-      </c>
       <c r="AE104">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF104">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG104">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17427,13 +17427,13 @@
         <v>2.26</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P105">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="Q105">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R105">
         <v>2.3</v>
@@ -17448,40 +17448,40 @@
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W105">
         <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
         <v>4.33</v>
       </c>
       <c r="AA105">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB105">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC105">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD105">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF105">
         <v>1.53</v>
       </c>
       <c r="AG105">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17596,16 +17596,16 @@
         <v>3.04</v>
       </c>
       <c r="Q106">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R106">
         <v>2.15</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T106">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="U106">
         <v>2.53</v>
@@ -17620,16 +17620,16 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA106">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB106">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC106">
         <v>2.88</v>
@@ -17638,13 +17638,13 @@
         <v>1.32</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG106">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK106">
         <v>1.62</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O107">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="P107">
-        <v>6.29</v>
+        <v>5.2</v>
       </c>
       <c r="Q107">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R107">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T107">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U107">
         <v>2.36</v>
       </c>
       <c r="V107">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W107">
         <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z107">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA107">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB107">
         <v>2.15</v>
       </c>
       <c r="AC107">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AD107">
         <v>1.46</v>
       </c>
       <c r="AE107">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF107">
         <v>1.7</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.14</v>
       </c>
       <c r="AK107">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18109,31 +18109,31 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18251,7 +18251,7 @@
         <v>2.93</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S110">
         <v>1.32</v>
@@ -18260,13 +18260,13 @@
         <v>2.96</v>
       </c>
       <c r="U110">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
         <v>1.01</v>
@@ -18281,13 +18281,13 @@
         <v>1.8</v>
       </c>
       <c r="AB110">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC110">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD110">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE110">
         <v>1.12</v>
@@ -18296,7 +18296,7 @@
         <v>1.6</v>
       </c>
       <c r="AG110">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AK110">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18405,10 +18405,10 @@
         <v>1.8</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P111">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q111">
         <v>2.25</v>
@@ -18423,7 +18423,7 @@
         <v>3.5</v>
       </c>
       <c r="U111">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V111">
         <v>1.6</v>
@@ -18441,7 +18441,7 @@
         <v>5</v>
       </c>
       <c r="AA111">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB111">
         <v>2.25</v>
@@ -18453,13 +18453,13 @@
         <v>1.52</v>
       </c>
       <c r="AE111">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF111">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG111">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
         <v>1.94</v>
@@ -18574,22 +18574,22 @@
         <v>2.07</v>
       </c>
       <c r="Q112">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R112">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S112">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T112">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="U112">
         <v>2.25</v>
       </c>
       <c r="V112">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W112">
         <v>1.13</v>
@@ -18598,7 +18598,7 @@
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z112">
         <v>4.8</v>
@@ -18607,7 +18607,7 @@
         <v>1.57</v>
       </c>
       <c r="AB112">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC112">
         <v>2.33</v>
@@ -18622,7 +18622,7 @@
         <v>1.5</v>
       </c>
       <c r="AG112">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18731,22 +18731,22 @@
         <v>1.57</v>
       </c>
       <c r="O113">
-        <v>4.2</v>
+        <v>4.47</v>
       </c>
       <c r="P113">
-        <v>5.7</v>
+        <v>5.87</v>
       </c>
       <c r="Q113">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R113">
         <v>2.4</v>
       </c>
       <c r="S113">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T113">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U113">
         <v>2.25</v>
@@ -18755,37 +18755,37 @@
         <v>1.55</v>
       </c>
       <c r="W113">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA113">
         <v>1.58</v>
       </c>
       <c r="AB113">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AC113">
         <v>2.37</v>
       </c>
       <c r="AD113">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE113">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF113">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG113">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="O114">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P114">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="Q114">
         <v>1.87</v>
@@ -18912,25 +18912,25 @@
         <v>3.58</v>
       </c>
       <c r="U114">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V114">
         <v>1.61</v>
       </c>
       <c r="W114">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z114">
-        <v>5.04</v>
+        <v>4.9</v>
       </c>
       <c r="AA114">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB114">
         <v>2.37</v>
@@ -18948,7 +18948,7 @@
         <v>1.63</v>
       </c>
       <c r="AG114">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19063,22 +19063,22 @@
         <v>2.5</v>
       </c>
       <c r="Q115">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="R115">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S115">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T115">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U115">
         <v>2.38</v>
       </c>
       <c r="V115">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W115">
         <v>1.09</v>
@@ -19090,19 +19090,19 @@
         <v>1.18</v>
       </c>
       <c r="Z115">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA115">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB115">
         <v>2.15</v>
       </c>
       <c r="AC115">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE115">
         <v>1.13</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK115">
         <v>1.47</v>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O116">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P116">
         <v>3</v>
@@ -19229,49 +19229,49 @@
         <v>2.5</v>
       </c>
       <c r="R116">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S116">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T116">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U116">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="V116">
         <v>1.72</v>
       </c>
       <c r="W116">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X116">
         <v>0</v>
       </c>
       <c r="Y116">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z116">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA116">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB116">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AC116">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD116">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE116">
         <v>1.29</v>
       </c>
       <c r="AF116">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG116">
         <v>2.9</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK116">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,61 +19380,61 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O117">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="P117">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="Q117">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="R117">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="S117">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T117">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U117">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V117">
         <v>1.36</v>
       </c>
       <c r="W117">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z117">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA117">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB117">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC117">
         <v>3.2</v>
       </c>
       <c r="AD117">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
         <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG117">
         <v>1.97</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK117">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19570,7 +19570,7 @@
         <v>1.35</v>
       </c>
       <c r="W118">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
         <v>1.01</v>
@@ -19579,28 +19579,28 @@
         <v>1.28</v>
       </c>
       <c r="Z118">
+        <v>3.25</v>
+      </c>
+      <c r="AA118">
+        <v>1.98</v>
+      </c>
+      <c r="AB118">
+        <v>1.74</v>
+      </c>
+      <c r="AC118">
         <v>3.05</v>
       </c>
-      <c r="AA118">
-        <v>1.99</v>
-      </c>
-      <c r="AB118">
-        <v>1.72</v>
-      </c>
-      <c r="AC118">
-        <v>3.42</v>
-      </c>
       <c r="AD118">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19706,25 +19706,25 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O119">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="P119">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q119">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R119">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S119">
         <v>1.33</v>
       </c>
       <c r="T119">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U119">
         <v>2.59</v>
@@ -19739,22 +19739,22 @@
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z119">
         <v>3.48</v>
       </c>
       <c r="AA119">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB119">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC119">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="AD119">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE119">
         <v>1.08</v>
@@ -19763,7 +19763,7 @@
         <v>1.66</v>
       </c>
       <c r="AG119">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK119">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,31 +19869,31 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="O120">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P120">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="Q120">
         <v>2.14</v>
       </c>
       <c r="R120">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S120">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T120">
         <v>4</v>
       </c>
       <c r="U120">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V120">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W120">
         <v>1.14</v>
@@ -19902,31 +19902,31 @@
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z120">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA120">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB120">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AC120">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD120">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE120">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF120">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AG120">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK120">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20035,31 +20035,31 @@
         <v>1.2</v>
       </c>
       <c r="O121">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="P121">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q121">
         <v>1.51</v>
       </c>
       <c r="R121">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="S121">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T121">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="U121">
         <v>1.75</v>
       </c>
       <c r="V121">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X121">
         <v>0</v>
@@ -20074,16 +20074,16 @@
         <v>1.25</v>
       </c>
       <c r="AB121">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AC121">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD121">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AE121">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF121">
         <v>1.77</v>
@@ -20105,7 +20105,7 @@
         <v>1.08</v>
       </c>
       <c r="AK121">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,25 +20195,25 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="O122">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
         <v>2.5</v>
       </c>
       <c r="Q122">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R122">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S122">
         <v>1.22</v>
       </c>
       <c r="T122">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U122">
         <v>2.1</v>
@@ -20222,22 +20222,22 @@
         <v>1.67</v>
       </c>
       <c r="W122">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X122">
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z122">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA122">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB122">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC122">
         <v>2.05</v>
@@ -20246,13 +20246,13 @@
         <v>1.73</v>
       </c>
       <c r="AE122">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF122">
         <v>1.4</v>
       </c>
       <c r="AG122">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
+        <v>1.85</v>
+      </c>
+      <c r="AC12">
+        <v>2.95</v>
+      </c>
+      <c r="AD12">
+        <v>1.29</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
         <v>1.7</v>
       </c>
-      <c r="AC12">
-        <v>3.5</v>
-      </c>
-      <c r="AD12">
-        <v>1.22</v>
-      </c>
-      <c r="AE12">
-        <v>1.04</v>
-      </c>
-      <c r="AF12">
-        <v>1.75</v>
-      </c>
       <c r="AG12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="S20">
+        <v>1.21</v>
+      </c>
+      <c r="T20">
+        <v>3.68</v>
+      </c>
+      <c r="U20">
+        <v>2.05</v>
+      </c>
+      <c r="V20">
+        <v>1.69</v>
+      </c>
+      <c r="W20">
+        <v>1.17</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.09</v>
+      </c>
+      <c r="Z20">
+        <v>9.4</v>
+      </c>
+      <c r="AA20">
+        <v>1.44</v>
+      </c>
+      <c r="AB20">
+        <v>2.7</v>
+      </c>
+      <c r="AC20">
+        <v>2.09</v>
+      </c>
+      <c r="AD20">
+        <v>1.76</v>
+      </c>
+      <c r="AE20">
         <v>1.29</v>
       </c>
-      <c r="T20">
-        <v>3.22</v>
-      </c>
-      <c r="U20">
-        <v>2.36</v>
-      </c>
-      <c r="V20">
-        <v>1.51</v>
-      </c>
-      <c r="W20">
-        <v>1.11</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>1.18</v>
-      </c>
-      <c r="Z20">
-        <v>5.48</v>
-      </c>
-      <c r="AA20">
-        <v>1.65</v>
-      </c>
-      <c r="AB20">
-        <v>2.2</v>
-      </c>
-      <c r="AC20">
-        <v>2.66</v>
-      </c>
-      <c r="AD20">
+      <c r="AF20">
+        <v>1.36</v>
+      </c>
+      <c r="AG20">
+        <v>2.89</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.45</v>
       </c>
-      <c r="AE20">
-        <v>1.14</v>
-      </c>
-      <c r="AF20">
-        <v>1.54</v>
-      </c>
-      <c r="AG20">
-        <v>2.3</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.28</v>
-      </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
+        <v>2.22</v>
+      </c>
+      <c r="S21">
+        <v>1.29</v>
+      </c>
+      <c r="T21">
+        <v>3.22</v>
+      </c>
+      <c r="U21">
         <v>2.36</v>
       </c>
-      <c r="S21">
-        <v>1.21</v>
-      </c>
-      <c r="T21">
-        <v>3.68</v>
-      </c>
-      <c r="U21">
-        <v>2.05</v>
-      </c>
       <c r="V21">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>9.4</v>
+        <v>5.48</v>
       </c>
       <c r="AA21">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="AD21">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AG21">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.96</v>
+        <v>3.97</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P30">
-        <v>3.1</v>
+        <v>1.77</v>
       </c>
       <c r="Q30">
-        <v>2.53</v>
+        <v>4.62</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U30">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA30">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC30">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.97</v>
+        <v>2.83</v>
       </c>
       <c r="O31">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="Q31">
-        <v>4.62</v>
+        <v>3.4</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.68</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.14</v>
+      </c>
+      <c r="Z31">
+        <v>4.4</v>
+      </c>
+      <c r="AA31">
+        <v>1.57</v>
+      </c>
+      <c r="AB31">
+        <v>2.25</v>
+      </c>
+      <c r="AC31">
+        <v>2.35</v>
+      </c>
+      <c r="AD31">
+        <v>1.47</v>
+      </c>
+      <c r="AE31">
+        <v>1.16</v>
+      </c>
+      <c r="AF31">
+        <v>1.47</v>
+      </c>
+      <c r="AG31">
+        <v>2.45</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.22</v>
       </c>
-      <c r="Z31">
-        <v>3.75</v>
-      </c>
-      <c r="AA31">
-        <v>1.77</v>
-      </c>
-      <c r="AB31">
-        <v>1.94</v>
-      </c>
-      <c r="AC31">
-        <v>2.83</v>
-      </c>
-      <c r="AD31">
+      <c r="AK31">
         <v>1.37</v>
-      </c>
-      <c r="AE31">
-        <v>1.1</v>
-      </c>
-      <c r="AF31">
-        <v>1.7</v>
-      </c>
-      <c r="AG31">
-        <v>2</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.18</v>
-      </c>
-      <c r="AK31">
-        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.83</v>
+        <v>1.96</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="Q32">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="R32">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
+        <v>1.69</v>
+      </c>
+      <c r="AB32">
+        <v>2.07</v>
+      </c>
+      <c r="AC32">
+        <v>2.8</v>
+      </c>
+      <c r="AD32">
+        <v>1.41</v>
+      </c>
+      <c r="AE32">
+        <v>1.13</v>
+      </c>
+      <c r="AF32">
         <v>1.57</v>
       </c>
-      <c r="AB32">
-        <v>2.25</v>
-      </c>
-      <c r="AC32">
-        <v>2.35</v>
-      </c>
-      <c r="AD32">
-        <v>1.47</v>
-      </c>
-      <c r="AE32">
-        <v>1.16</v>
-      </c>
-      <c r="AF32">
-        <v>1.47</v>
-      </c>
       <c r="AG32">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -11070,58 +11070,58 @@
         <v>1.67</v>
       </c>
       <c r="O66">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P66">
         <v>5.5</v>
       </c>
       <c r="Q66">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R66">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S66">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T66">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U66">
         <v>4.05</v>
       </c>
       <c r="V66">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W66">
         <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y66">
         <v>1.65</v>
       </c>
       <c r="Z66">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AA66">
         <v>3.07</v>
       </c>
       <c r="AB66">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC66">
-        <v>5.95</v>
+        <v>6.41</v>
       </c>
       <c r="AD66">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE66">
         <v>1.02</v>
       </c>
       <c r="AF66">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AG66">
         <v>1.4</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O67">
         <v>2.8</v>
@@ -13195,7 +13195,7 @@
         <v>3.75</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R79">
         <v>1.83</v>
@@ -13207,10 +13207,10 @@
         <v>2.04</v>
       </c>
       <c r="U79">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V79">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W79">
         <v>1.03</v>
@@ -13228,7 +13228,7 @@
         <v>3.08</v>
       </c>
       <c r="AB79">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC79">
         <v>6.75</v>
@@ -13243,7 +13243,7 @@
         <v>2.5</v>
       </c>
       <c r="AG79">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
+        <v>2.8</v>
+      </c>
+      <c r="P90">
+        <v>4</v>
+      </c>
+      <c r="Q90">
         <v>2.75</v>
-      </c>
-      <c r="P90">
-        <v>4.33</v>
-      </c>
-      <c r="Q90">
-        <v>2.84</v>
       </c>
       <c r="R90">
         <v>1.74</v>
       </c>
       <c r="S90">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T90">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="U90">
         <v>4.3</v>
@@ -15036,7 +15036,7 @@
         <v>2.51</v>
       </c>
       <c r="AG90">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O94">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P94">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="Q94">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="R94">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="U94">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="V94">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W94">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>4.09</v>
+        <v>3.68</v>
       </c>
       <c r="AA94">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB94">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD94">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE94">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG94">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O95">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="P95">
-        <v>2.31</v>
+        <v>3.75</v>
       </c>
       <c r="Q95">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="R95">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S95">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="T95">
-        <v>2.44</v>
+        <v>3.32</v>
       </c>
       <c r="U95">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="V95">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X95">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
+        <v>1.16</v>
+      </c>
+      <c r="Z95">
+        <v>4.09</v>
+      </c>
+      <c r="AA95">
+        <v>1.65</v>
+      </c>
+      <c r="AB95">
+        <v>2.14</v>
+      </c>
+      <c r="AC95">
+        <v>2.56</v>
+      </c>
+      <c r="AD95">
         <v>1.4</v>
       </c>
-      <c r="Z95">
-        <v>2.66</v>
-      </c>
-      <c r="AA95">
-        <v>2.23</v>
-      </c>
-      <c r="AB95">
-        <v>1.58</v>
-      </c>
-      <c r="AC95">
-        <v>3.98</v>
-      </c>
-      <c r="AD95">
-        <v>1.17</v>
-      </c>
       <c r="AE95">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AG95">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK95">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="P96">
-        <v>4.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q96">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="R96">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S96">
+        <v>1.46</v>
+      </c>
+      <c r="T96">
+        <v>2.44</v>
+      </c>
+      <c r="U96">
+        <v>3.1</v>
+      </c>
+      <c r="V96">
+        <v>1.29</v>
+      </c>
+      <c r="W96">
+        <v>1.06</v>
+      </c>
+      <c r="X96">
+        <v>1.04</v>
+      </c>
+      <c r="Y96">
+        <v>1.4</v>
+      </c>
+      <c r="Z96">
+        <v>2.66</v>
+      </c>
+      <c r="AA96">
+        <v>2.23</v>
+      </c>
+      <c r="AB96">
+        <v>1.58</v>
+      </c>
+      <c r="AC96">
+        <v>3.98</v>
+      </c>
+      <c r="AD96">
+        <v>1.17</v>
+      </c>
+      <c r="AE96">
+        <v>1.02</v>
+      </c>
+      <c r="AF96">
+        <v>1.89</v>
+      </c>
+      <c r="AG96">
+        <v>1.76</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.3</v>
       </c>
-      <c r="T96">
-        <v>3.08</v>
-      </c>
-      <c r="U96">
-        <v>2.47</v>
-      </c>
-      <c r="V96">
-        <v>1.45</v>
-      </c>
-      <c r="W96">
-        <v>1.08</v>
-      </c>
-      <c r="X96">
-        <v>1</v>
-      </c>
-      <c r="Y96">
-        <v>1.2</v>
-      </c>
-      <c r="Z96">
-        <v>3.68</v>
-      </c>
-      <c r="AA96">
-        <v>1.75</v>
-      </c>
-      <c r="AB96">
-        <v>2.05</v>
-      </c>
-      <c r="AC96">
-        <v>2.74</v>
-      </c>
-      <c r="AD96">
-        <v>1.35</v>
-      </c>
-      <c r="AE96">
-        <v>1.11</v>
-      </c>
-      <c r="AF96">
-        <v>1.76</v>
-      </c>
-      <c r="AG96">
-        <v>1.94</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.17</v>
-      </c>
       <c r="AK96">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O102">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>3.88</v>
+        <v>2.6</v>
       </c>
       <c r="Q102">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
         <v>1.29</v>
       </c>
       <c r="T102">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U102">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V102">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z102">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA102">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC102">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD102">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG102">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P103">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="Q103">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T103">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="V103">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W103">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB103">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC103">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD103">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE103">
         <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P104">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="Q104">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="R104">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S104">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="U104">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="V104">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
+        <v>1.23</v>
+      </c>
+      <c r="Z104">
+        <v>4</v>
+      </c>
+      <c r="AA104">
+        <v>1.75</v>
+      </c>
+      <c r="AB104">
+        <v>2</v>
+      </c>
+      <c r="AC104">
+        <v>2.88</v>
+      </c>
+      <c r="AD104">
+        <v>1.38</v>
+      </c>
+      <c r="AE104">
         <v>1.11</v>
       </c>
-      <c r="Z104">
-        <v>5.2</v>
-      </c>
-      <c r="AA104">
-        <v>1.5</v>
-      </c>
-      <c r="AB104">
-        <v>2.4</v>
-      </c>
-      <c r="AC104">
-        <v>2.25</v>
-      </c>
-      <c r="AD104">
-        <v>1.57</v>
-      </c>
-      <c r="AE104">
-        <v>1.2</v>
-      </c>
       <c r="AF104">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG104">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK104">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,65 +17424,65 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="O105">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>3.06</v>
+        <v>2</v>
       </c>
       <c r="Q105">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R105">
         <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T105">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="U105">
+        <v>2.15</v>
+      </c>
+      <c r="V105">
+        <v>1.6</v>
+      </c>
+      <c r="W105">
+        <v>1.13</v>
+      </c>
+      <c r="X105">
+        <v>1.01</v>
+      </c>
+      <c r="Y105">
+        <v>1.11</v>
+      </c>
+      <c r="Z105">
+        <v>5.2</v>
+      </c>
+      <c r="AA105">
+        <v>1.5</v>
+      </c>
+      <c r="AB105">
+        <v>2.4</v>
+      </c>
+      <c r="AC105">
+        <v>2.25</v>
+      </c>
+      <c r="AD105">
+        <v>1.57</v>
+      </c>
+      <c r="AE105">
+        <v>1.2</v>
+      </c>
+      <c r="AF105">
+        <v>1.47</v>
+      </c>
+      <c r="AG105">
         <v>2.55</v>
       </c>
-      <c r="V105">
-        <v>1.45</v>
-      </c>
-      <c r="W105">
-        <v>1.1</v>
-      </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.2</v>
-      </c>
-      <c r="Z105">
-        <v>4.33</v>
-      </c>
-      <c r="AA105">
-        <v>1.71</v>
-      </c>
-      <c r="AB105">
-        <v>2.08</v>
-      </c>
-      <c r="AC105">
-        <v>2.75</v>
-      </c>
-      <c r="AD105">
-        <v>1.42</v>
-      </c>
-      <c r="AE105">
-        <v>1.14</v>
-      </c>
-      <c r="AF105">
-        <v>1.53</v>
-      </c>
-      <c r="AG105">
-        <v>2.31</v>
-      </c>
       <c r="AH105" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
+        <v>2.24</v>
+      </c>
+      <c r="Q8">
+        <v>3.39</v>
+      </c>
+      <c r="R8">
+        <v>1.88</v>
+      </c>
+      <c r="S8">
+        <v>1.42</v>
+      </c>
+      <c r="T8">
+        <v>2.56</v>
+      </c>
+      <c r="U8">
+        <v>3.34</v>
+      </c>
+      <c r="V8">
+        <v>1.28</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.43</v>
+      </c>
+      <c r="Z8">
+        <v>2.81</v>
+      </c>
+      <c r="AA8">
         <v>2.3</v>
       </c>
-      <c r="Q8">
-        <v>3.31</v>
-      </c>
-      <c r="R8">
-        <v>2.05</v>
-      </c>
-      <c r="S8">
-        <v>1.39</v>
-      </c>
-      <c r="T8">
-        <v>2.7</v>
-      </c>
-      <c r="U8">
-        <v>2.73</v>
-      </c>
-      <c r="V8">
-        <v>1.4</v>
-      </c>
-      <c r="W8">
-        <v>1.06</v>
-      </c>
-      <c r="X8">
+      <c r="AB8">
+        <v>1.6</v>
+      </c>
+      <c r="AC8">
+        <v>4.2</v>
+      </c>
+      <c r="AD8">
+        <v>1.16</v>
+      </c>
+      <c r="AE8">
         <v>1.01</v>
       </c>
-      <c r="Y8">
-        <v>1.25</v>
-      </c>
-      <c r="Z8">
-        <v>3.3</v>
-      </c>
-      <c r="AA8">
-        <v>1.96</v>
-      </c>
-      <c r="AB8">
-        <v>1.88</v>
-      </c>
-      <c r="AC8">
-        <v>3.25</v>
-      </c>
-      <c r="AD8">
-        <v>1.29</v>
-      </c>
-      <c r="AE8">
-        <v>1.08</v>
-      </c>
       <c r="AF8">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>1.39</v>
+      </c>
+      <c r="T9">
+        <v>2.7</v>
+      </c>
+      <c r="U9">
+        <v>2.73</v>
+      </c>
+      <c r="V9">
+        <v>1.4</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.25</v>
+      </c>
+      <c r="Z9">
+        <v>3.3</v>
+      </c>
+      <c r="AA9">
+        <v>1.96</v>
+      </c>
+      <c r="AB9">
         <v>1.88</v>
       </c>
-      <c r="S9">
-        <v>1.42</v>
-      </c>
-      <c r="T9">
-        <v>2.56</v>
-      </c>
-      <c r="U9">
-        <v>3.34</v>
-      </c>
-      <c r="V9">
-        <v>1.28</v>
-      </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
-      <c r="Y9">
-        <v>1.43</v>
-      </c>
-      <c r="Z9">
-        <v>2.81</v>
-      </c>
-      <c r="AA9">
-        <v>2.3</v>
-      </c>
-      <c r="AB9">
-        <v>1.6</v>
-      </c>
       <c r="AC9">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O66">
         <v>3</v>
       </c>
       <c r="P66">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q66">
         <v>2.3</v>
@@ -11088,7 +11088,7 @@
         <v>2.15</v>
       </c>
       <c r="U66">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="V66">
         <v>1.22</v>
@@ -11121,7 +11121,7 @@
         <v>1.02</v>
       </c>
       <c r="AF66">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AG66">
         <v>1.4</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O85">
         <v>4.5</v>
       </c>
       <c r="P85">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14339,25 +14339,25 @@
         <v>2.62</v>
       </c>
       <c r="R86">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T86">
         <v>2.44</v>
       </c>
       <c r="U86">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V86">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W86">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X86">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
         <v>1.39</v>
@@ -14366,16 +14366,16 @@
         <v>2.61</v>
       </c>
       <c r="AA86">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB86">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC86">
         <v>4.5</v>
       </c>
       <c r="AD86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE86">
         <v>1.01</v>
@@ -14384,7 +14384,7 @@
         <v>2.06</v>
       </c>
       <c r="AG86">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15021,7 +15021,7 @@
         <v>3.11</v>
       </c>
       <c r="AB90">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC90">
         <v>6.55</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="O92">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P92">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15477,25 +15477,25 @@
         <v>1.67</v>
       </c>
       <c r="Q93">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U93">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V93">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15507,13 +15507,13 @@
         <v>3.96</v>
       </c>
       <c r="AA93">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AB93">
         <v>2.08</v>
       </c>
       <c r="AC93">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD93">
         <v>1.39</v>
@@ -15525,7 +15525,7 @@
         <v>1.65</v>
       </c>
       <c r="AG93">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="AK93">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,16 +15631,16 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="O94">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P94">
-        <v>4.45</v>
+        <v>4.95</v>
       </c>
       <c r="Q94">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R94">
         <v>2.3</v>
@@ -15649,7 +15649,7 @@
         <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U94">
         <v>2.47</v>
@@ -15673,7 +15673,7 @@
         <v>1.75</v>
       </c>
       <c r="AB94">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC94">
         <v>2.74</v>
@@ -15685,10 +15685,10 @@
         <v>1.11</v>
       </c>
       <c r="AF94">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG94">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15794,34 +15794,34 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="O95">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P95">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q95">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S95">
         <v>1.26</v>
       </c>
       <c r="T95">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U95">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15833,10 +15833,10 @@
         <v>4.09</v>
       </c>
       <c r="AA95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB95">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC95">
         <v>2.56</v>
@@ -15845,7 +15845,7 @@
         <v>1.4</v>
       </c>
       <c r="AE95">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF95">
         <v>1.61</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK95">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15960,10 +15960,10 @@
         <v>2.5</v>
       </c>
       <c r="O96">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="P96">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
         <v>3.4</v>
@@ -15975,16 +15975,16 @@
         <v>1.46</v>
       </c>
       <c r="T96">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U96">
         <v>3.1</v>
       </c>
       <c r="V96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W96">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X96">
         <v>1.04</v>
@@ -15996,13 +15996,13 @@
         <v>2.66</v>
       </c>
       <c r="AA96">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB96">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC96">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AD96">
         <v>1.17</v>
@@ -16014,7 +16014,7 @@
         <v>1.89</v>
       </c>
       <c r="AG96">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16292,10 +16292,10 @@
         <v>4.28</v>
       </c>
       <c r="Q98">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R98">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="S98">
         <v>1.4</v>
@@ -16337,10 +16337,10 @@
         <v>1.06</v>
       </c>
       <c r="AF98">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG98">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK98">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P102">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T102">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U102">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="V102">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W102">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z102">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB102">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC102">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD102">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE102">
         <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG102">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,65 +17098,65 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="O103">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>3.06</v>
+        <v>2</v>
       </c>
       <c r="Q103">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R103">
         <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T103">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="U103">
+        <v>2.15</v>
+      </c>
+      <c r="V103">
+        <v>1.6</v>
+      </c>
+      <c r="W103">
+        <v>1.13</v>
+      </c>
+      <c r="X103">
+        <v>1.01</v>
+      </c>
+      <c r="Y103">
+        <v>1.11</v>
+      </c>
+      <c r="Z103">
+        <v>5.2</v>
+      </c>
+      <c r="AA103">
+        <v>1.5</v>
+      </c>
+      <c r="AB103">
+        <v>2.4</v>
+      </c>
+      <c r="AC103">
+        <v>2.25</v>
+      </c>
+      <c r="AD103">
+        <v>1.57</v>
+      </c>
+      <c r="AE103">
+        <v>1.2</v>
+      </c>
+      <c r="AF103">
+        <v>1.47</v>
+      </c>
+      <c r="AG103">
         <v>2.55</v>
       </c>
-      <c r="V103">
-        <v>1.45</v>
-      </c>
-      <c r="W103">
-        <v>1.1</v>
-      </c>
-      <c r="X103">
-        <v>1.02</v>
-      </c>
-      <c r="Y103">
-        <v>1.2</v>
-      </c>
-      <c r="Z103">
-        <v>4.33</v>
-      </c>
-      <c r="AA103">
-        <v>1.71</v>
-      </c>
-      <c r="AB103">
-        <v>2.08</v>
-      </c>
-      <c r="AC103">
-        <v>2.75</v>
-      </c>
-      <c r="AD103">
-        <v>1.42</v>
-      </c>
-      <c r="AE103">
-        <v>1.14</v>
-      </c>
-      <c r="AF103">
-        <v>1.53</v>
-      </c>
-      <c r="AG103">
-        <v>2.31</v>
-      </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>3.88</v>
+        <v>2.6</v>
       </c>
       <c r="Q104">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S104">
         <v>1.29</v>
       </c>
       <c r="T104">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U104">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V104">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W104">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z104">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA104">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB104">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC104">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD104">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG104">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P105">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="Q105">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="R105">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S105">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="U105">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="V105">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
+        <v>1.23</v>
+      </c>
+      <c r="Z105">
+        <v>4</v>
+      </c>
+      <c r="AA105">
+        <v>1.75</v>
+      </c>
+      <c r="AB105">
+        <v>2</v>
+      </c>
+      <c r="AC105">
+        <v>2.88</v>
+      </c>
+      <c r="AD105">
+        <v>1.38</v>
+      </c>
+      <c r="AE105">
         <v>1.11</v>
       </c>
-      <c r="Z105">
-        <v>5.2</v>
-      </c>
-      <c r="AA105">
-        <v>1.5</v>
-      </c>
-      <c r="AB105">
-        <v>2.4</v>
-      </c>
-      <c r="AC105">
-        <v>2.25</v>
-      </c>
-      <c r="AD105">
-        <v>1.57</v>
-      </c>
-      <c r="AE105">
-        <v>1.2</v>
-      </c>
       <c r="AF105">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK105">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18260,13 +18260,13 @@
         <v>2.96</v>
       </c>
       <c r="U110">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>1.01</v>
@@ -18275,13 +18275,13 @@
         <v>1.21</v>
       </c>
       <c r="Z110">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="AA110">
         <v>1.8</v>
       </c>
       <c r="AB110">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC110">
         <v>2.78</v>
@@ -18290,13 +18290,13 @@
         <v>1.34</v>
       </c>
       <c r="AE110">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG110">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AK110">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="O114">
         <v>4.3</v>
       </c>
       <c r="P114">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q114">
         <v>1.87</v>
@@ -18906,10 +18906,10 @@
         <v>2.67</v>
       </c>
       <c r="S114">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T114">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U114">
         <v>2.17</v>
@@ -18924,7 +18924,7 @@
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z114">
         <v>4.9</v>
@@ -18933,7 +18933,7 @@
         <v>1.46</v>
       </c>
       <c r="AB114">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC114">
         <v>2.25</v>
@@ -18942,13 +18942,13 @@
         <v>1.57</v>
       </c>
       <c r="AE114">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF114">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG114">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>2.75</v>
       </c>
       <c r="R115">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
         <v>1.28</v>
@@ -19093,16 +19093,16 @@
         <v>3.9</v>
       </c>
       <c r="AA115">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB115">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC115">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AD115">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE115">
         <v>1.13</v>
@@ -19380,34 +19380,34 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O117">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P117">
         <v>2.71</v>
       </c>
       <c r="Q117">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R117">
         <v>2.09</v>
       </c>
       <c r="S117">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T117">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U117">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V117">
         <v>1.36</v>
       </c>
       <c r="W117">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X117">
         <v>1.01</v>
@@ -19416,16 +19416,16 @@
         <v>1.25</v>
       </c>
       <c r="Z117">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AA117">
         <v>1.9</v>
       </c>
       <c r="AB117">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC117">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD117">
         <v>1.25</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O118">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P118">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q118">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R118">
         <v>2.05</v>
@@ -19561,7 +19561,7 @@
         <v>1.38</v>
       </c>
       <c r="T118">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U118">
         <v>2.82</v>
@@ -19579,10 +19579,10 @@
         <v>1.28</v>
       </c>
       <c r="Z118">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA118">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB118">
         <v>1.74</v>
@@ -19591,7 +19591,7 @@
         <v>3.05</v>
       </c>
       <c r="AD118">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE118">
         <v>1.05</v>
@@ -19600,7 +19600,7 @@
         <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK118">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,49 +19715,49 @@
         <v>2.77</v>
       </c>
       <c r="Q119">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R119">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
         <v>1.33</v>
       </c>
       <c r="T119">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U119">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V119">
         <v>1.41</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X119">
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z119">
         <v>3.48</v>
       </c>
       <c r="AA119">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB119">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC119">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AD119">
         <v>1.3</v>
       </c>
       <c r="AE119">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF119">
         <v>1.66</v>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK119">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -2594,16 +2594,16 @@
         <v>1.38</v>
       </c>
       <c r="O14">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="Q14">
         <v>1.91</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
       <c r="S14">
         <v>1.31</v>
@@ -2624,13 +2624,13 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
         <v>4.2</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB14">
         <v>2.2</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
         <v>2.87</v>
@@ -4073,16 +4073,16 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4091,16 +4091,16 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA23">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
         <v>3.15</v>
@@ -4112,10 +4112,10 @@
         <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG23">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK23">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>3.15</v>
+        <v>3.72</v>
       </c>
       <c r="Q24">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
         <v>2.77</v>
       </c>
       <c r="U24">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
         <v>1.06</v>
@@ -4278,7 +4278,7 @@
         <v>1.76</v>
       </c>
       <c r="AG24">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
         <v>1.8</v>
@@ -4393,16 +4393,16 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="R25">
         <v>1.93</v>
       </c>
       <c r="S25">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T25">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U25">
         <v>3.16</v>
@@ -4417,31 +4417,31 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AA25">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AB25">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC25">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="AD25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
         <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AG25">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>3.65</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
         <v>1.08</v>
@@ -4930,7 +4930,7 @@
         <v>1.69</v>
       </c>
       <c r="AG28">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="O29">
         <v>4.75</v>
       </c>
       <c r="P29">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Q29">
-        <v>7.83</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="S29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="U29">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="AA29">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB29">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AD29">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE29">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
         <v>1.85</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>2.9</v>
       </c>
       <c r="AK29">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="O30">
         <v>3.54</v>
       </c>
       <c r="P30">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q30">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="R30">
         <v>2.15</v>
@@ -5217,10 +5217,10 @@
         <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="U30">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="V30">
         <v>1.44</v>
@@ -5229,7 +5229,7 @@
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.22</v>
@@ -5238,10 +5238,10 @@
         <v>3.75</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB30">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC30">
         <v>2.83</v>
@@ -5250,13 +5250,13 @@
         <v>1.37</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
         <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="AK30">
         <v>1.14</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q31">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
         <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5404,7 +5404,7 @@
         <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
         <v>2.35</v>
@@ -5416,7 +5416,7 @@
         <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
         <v>2.45</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AK31">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="O32">
         <v>3.4</v>
@@ -5534,10 +5534,10 @@
         <v>3.1</v>
       </c>
       <c r="Q32">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="R32">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.27</v>
@@ -5549,13 +5549,13 @@
         <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.19</v>
@@ -5567,19 +5567,19 @@
         <v>1.69</v>
       </c>
       <c r="AB32">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC32">
         <v>2.8</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
         <v>2.19</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5730,7 +5730,7 @@
         <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC33">
         <v>3.34</v>
@@ -5745,7 +5745,7 @@
         <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AK33">
         <v>1.31</v>
@@ -6186,37 +6186,37 @@
         <v>3.86</v>
       </c>
       <c r="Q36">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="R36">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AA36">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB36">
         <v>1.7</v>
@@ -6228,13 +6228,13 @@
         <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AB40">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q41">
-        <v>2.01</v>
+        <v>2.73</v>
       </c>
       <c r="R41">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>3.03</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA41">
+        <v>2.1</v>
+      </c>
+      <c r="AB41">
+        <v>1.79</v>
+      </c>
+      <c r="AC41">
+        <v>3.7</v>
+      </c>
+      <c r="AD41">
+        <v>1.22</v>
+      </c>
+      <c r="AE41">
+        <v>1.06</v>
+      </c>
+      <c r="AF41">
         <v>1.71</v>
       </c>
-      <c r="AB41">
-        <v>2.1</v>
-      </c>
-      <c r="AC41">
-        <v>2.56</v>
-      </c>
-      <c r="AD41">
-        <v>1.4</v>
-      </c>
-      <c r="AE41">
-        <v>1.12</v>
-      </c>
-      <c r="AF41">
-        <v>1.72</v>
-      </c>
       <c r="AG41">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7167,7 +7167,7 @@
         <v>2.7</v>
       </c>
       <c r="R42">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
         <v>1.3</v>
@@ -7191,7 +7191,7 @@
         <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
@@ -7200,19 +7200,19 @@
         <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
         <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P43">
-        <v>4.28</v>
+        <v>3.65</v>
       </c>
       <c r="Q43">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="R43">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T43">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
         <v>2.72</v>
@@ -7351,31 +7351,31 @@
         <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA43">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD43">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG43">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7674,13 +7674,13 @@
         <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y45">
         <v>1.52</v>
       </c>
       <c r="Z45">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AA45">
         <v>2.64</v>
@@ -7689,7 +7689,7 @@
         <v>1.51</v>
       </c>
       <c r="AC45">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AD45">
         <v>1.14</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8133,49 +8133,49 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q48">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R48">
         <v>2.34</v>
       </c>
       <c r="S48">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z48">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA48">
         <v>1.47</v>
       </c>
       <c r="AB48">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC48">
         <v>2.11</v>
@@ -8184,13 +8184,13 @@
         <v>1.7</v>
       </c>
       <c r="AE48">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF48">
         <v>1.38</v>
       </c>
       <c r="AG48">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
         <v>1.53</v>
@@ -8299,13 +8299,13 @@
         <v>1.89</v>
       </c>
       <c r="O49">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R49">
         <v>2.3</v>
@@ -8317,13 +8317,13 @@
         <v>3.45</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V49">
         <v>1.6</v>
       </c>
       <c r="W49">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1.03</v>
@@ -8338,13 +8338,13 @@
         <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AC49">
         <v>2.38</v>
       </c>
       <c r="AD49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE49">
         <v>1.16</v>
@@ -8353,7 +8353,7 @@
         <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>1.92</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC50">
         <v>3.05</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,43 +8785,43 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O52">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q52">
-        <v>4.02</v>
+        <v>3.52</v>
       </c>
       <c r="R52">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S52">
         <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
         <v>1.85</v>
@@ -8830,7 +8830,7 @@
         <v>1.85</v>
       </c>
       <c r="AC52">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD52">
         <v>1.28</v>
@@ -8839,10 +8839,10 @@
         <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,34 +8948,34 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
         <v>3.22</v>
       </c>
       <c r="U53">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
         <v>1.04</v>
@@ -8984,13 +8984,13 @@
         <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC53">
         <v>2.63</v>
@@ -8999,13 +8999,13 @@
         <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.08</v>
@@ -9159,7 +9159,7 @@
         <v>3.04</v>
       </c>
       <c r="AD54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
         <v>1.11</v>
@@ -9609,10 +9609,10 @@
         <v>1.99</v>
       </c>
       <c r="Q57">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="R57">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
         <v>1.39</v>
@@ -9621,43 +9621,43 @@
         <v>2.63</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V57">
         <v>1.33</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB57">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC57">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG57">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AK57">
         <v>1.25</v>
@@ -9772,34 +9772,34 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R58">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="V58">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W58">
         <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z58">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
         <v>2.1</v>
@@ -9808,13 +9808,13 @@
         <v>1.64</v>
       </c>
       <c r="AC58">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="AD58">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
         <v>1.82</v>
@@ -9836,7 +9836,7 @@
         <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,25 +9935,25 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="R59">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
+        <v>1.33</v>
+      </c>
+      <c r="T59">
+        <v>3</v>
+      </c>
+      <c r="U59">
+        <v>2.75</v>
+      </c>
+      <c r="V59">
         <v>1.36</v>
       </c>
-      <c r="T59">
-        <v>2.75</v>
-      </c>
-      <c r="U59">
-        <v>2.88</v>
-      </c>
-      <c r="V59">
-        <v>1.35</v>
-      </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,10 +9965,10 @@
         <v>3.28</v>
       </c>
       <c r="AA59">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB59">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC59">
         <v>3.2</v>
@@ -9999,7 +9999,7 @@
         <v>1.24</v>
       </c>
       <c r="AK59">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O60">
         <v>3.08</v>
       </c>
       <c r="P60">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="Q60">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R60">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S60">
         <v>1.32</v>
@@ -10110,7 +10110,7 @@
         <v>2.96</v>
       </c>
       <c r="U60">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="V60">
         <v>1.39</v>
@@ -10122,19 +10122,19 @@
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z60">
         <v>3.42</v>
       </c>
       <c r="AA60">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB60">
         <v>1.87</v>
       </c>
       <c r="AC60">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD60">
         <v>1.28</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="O61">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P61">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O62">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="P62">
         <v>7.6</v>
@@ -10427,7 +10427,7 @@
         <v>1.68</v>
       </c>
       <c r="R62">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="S62">
         <v>1.21</v>
@@ -10460,19 +10460,19 @@
         <v>2.66</v>
       </c>
       <c r="AC62">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AD62">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE62">
         <v>1.26</v>
       </c>
       <c r="AF62">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG62">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK62">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O63">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q63">
         <v>3.15</v>
@@ -10599,16 +10599,16 @@
         <v>3</v>
       </c>
       <c r="U63">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V63">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
         <v>1.06</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
         <v>1.24</v>
@@ -10617,10 +10617,10 @@
         <v>3.34</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB63">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC63">
         <v>3.05</v>
@@ -10651,7 +10651,7 @@
         <v>1.23</v>
       </c>
       <c r="AK63">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,25 +10750,25 @@
         <v>3.47</v>
       </c>
       <c r="Q64">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
         <v>2.11</v>
       </c>
       <c r="S64">
+        <v>1.36</v>
+      </c>
+      <c r="T64">
+        <v>2.88</v>
+      </c>
+      <c r="U64">
+        <v>2.82</v>
+      </c>
+      <c r="V64">
         <v>1.35</v>
       </c>
-      <c r="T64">
-        <v>2.82</v>
-      </c>
-      <c r="U64">
-        <v>3</v>
-      </c>
-      <c r="V64">
-        <v>1.33</v>
-      </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10943,7 +10943,7 @@
         <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB65">
         <v>1.85</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
         <v>1.72</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="O68">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -11408,16 +11408,16 @@
         <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
         <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
         <v>1.12</v>
@@ -11432,10 +11432,10 @@
         <v>4</v>
       </c>
       <c r="AA68">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB68">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AC68">
         <v>2.7</v>
@@ -11447,10 +11447,10 @@
         <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11888,13 +11888,13 @@
         <v>4.2</v>
       </c>
       <c r="P71">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="Q71">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R71">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S71">
         <v>1.35</v>
@@ -11903,13 +11903,13 @@
         <v>2.87</v>
       </c>
       <c r="U71">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
         <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
         <v>1.01</v>
@@ -11921,10 +11921,10 @@
         <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC71">
         <v>2.75</v>
@@ -11936,10 +11936,10 @@
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG71">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,34 +12045,34 @@
         </is>
       </c>
       <c r="N72">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="O72">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P72">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q72">
-        <v>6.23</v>
+        <v>6</v>
       </c>
       <c r="R72">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T72">
         <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="V72">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12084,25 +12084,25 @@
         <v>3.92</v>
       </c>
       <c r="AA72">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB72">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC72">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD72">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG72">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>1.95</v>
+      </c>
+      <c r="O73">
+        <v>4.05</v>
+      </c>
+      <c r="P73">
+        <v>3</v>
+      </c>
+      <c r="Q73">
         <v>2.4</v>
       </c>
-      <c r="O73">
-        <v>3.7</v>
-      </c>
-      <c r="P73">
-        <v>2.78</v>
-      </c>
-      <c r="Q73">
-        <v>2.49</v>
-      </c>
       <c r="R73">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S73">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T73">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U73">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V73">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W73">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z73">
-        <v>5.8</v>
+        <v>6.36</v>
       </c>
       <c r="AA73">
         <v>1.36</v>
       </c>
       <c r="AB73">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="AC73">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD73">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE73">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF73">
         <v>1.36</v>
       </c>
       <c r="AG73">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK73">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -15142,58 +15142,58 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="O91">
         <v>3.6</v>
       </c>
       <c r="P91">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q91">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S91">
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U91">
         <v>2.2</v>
       </c>
       <c r="V91">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W91">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z91">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA91">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB91">
         <v>2.55</v>
       </c>
       <c r="AC91">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD91">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE91">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK91">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P92">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15468,61 +15468,61 @@
         </is>
       </c>
       <c r="N93">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="O93">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="P93">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q93">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R93">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U93">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W93">
         <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z93">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="AA93">
         <v>1.54</v>
       </c>
       <c r="AB93">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC93">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD93">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AE93">
         <v>1.17</v>
       </c>
       <c r="AF93">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG93">
         <v>2.08</v>
@@ -15637,10 +15637,10 @@
         <v>3.92</v>
       </c>
       <c r="P94">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="Q94">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="R94">
         <v>2.3</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="O95">
         <v>4.1</v>
       </c>
       <c r="P95">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -15830,7 +15830,7 @@
         <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
       <c r="AA95">
         <v>1.66</v>
@@ -15960,10 +15960,10 @@
         <v>2.5</v>
       </c>
       <c r="O96">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="Q96">
         <v>3.4</v>
@@ -16002,7 +16002,7 @@
         <v>1.61</v>
       </c>
       <c r="AC96">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD96">
         <v>1.17</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O97">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P97">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q97">
         <v>2.2</v>
       </c>
       <c r="R97">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S97">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T97">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U97">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V97">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W97">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X97">
         <v>0</v>
       </c>
       <c r="Y97">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z97">
         <v>7</v>
       </c>
       <c r="AA97">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB97">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AC97">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AD97">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE97">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF97">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG97">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK97">
         <v>2.05</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O100">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC101">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD101">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O102">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="Q102">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R102">
         <v>2.3</v>
       </c>
       <c r="S102">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="U102">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V102">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W102">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA102">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AC102">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD102">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE102">
         <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG102">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK102">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>2</v>
+        <v>3.57</v>
       </c>
       <c r="Q103">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="R103">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S103">
+        <v>1.35</v>
+      </c>
+      <c r="T103">
+        <v>3.3</v>
+      </c>
+      <c r="U103">
+        <v>2.55</v>
+      </c>
+      <c r="V103">
+        <v>1.45</v>
+      </c>
+      <c r="W103">
+        <v>1.07</v>
+      </c>
+      <c r="X103">
+        <v>1.05</v>
+      </c>
+      <c r="Y103">
         <v>1.23</v>
       </c>
-      <c r="T103">
-        <v>3.65</v>
-      </c>
-      <c r="U103">
-        <v>2.15</v>
-      </c>
-      <c r="V103">
-        <v>1.6</v>
-      </c>
-      <c r="W103">
-        <v>1.13</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
+      <c r="Z103">
+        <v>4</v>
+      </c>
+      <c r="AA103">
+        <v>1.75</v>
+      </c>
+      <c r="AB103">
+        <v>1.98</v>
+      </c>
+      <c r="AC103">
+        <v>2.88</v>
+      </c>
+      <c r="AD103">
+        <v>1.38</v>
+      </c>
+      <c r="AE103">
         <v>1.11</v>
       </c>
-      <c r="Z103">
-        <v>5.2</v>
-      </c>
-      <c r="AA103">
-        <v>1.5</v>
-      </c>
-      <c r="AB103">
-        <v>2.4</v>
-      </c>
-      <c r="AC103">
-        <v>2.25</v>
-      </c>
-      <c r="AD103">
-        <v>1.57</v>
-      </c>
-      <c r="AE103">
-        <v>1.2</v>
-      </c>
       <c r="AF103">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O104">
         <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="R104">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U104">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V104">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W104">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA104">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB104">
         <v>2.25</v>
       </c>
       <c r="AC104">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD104">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE104">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF104">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG104">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.92</v>
+        <v>2.95</v>
       </c>
       <c r="O105">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="P105">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="Q105">
-        <v>2.43</v>
+        <v>3.54</v>
       </c>
       <c r="R105">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="U105">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="V105">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z105">
-        <v>4</v>
+        <v>6.57</v>
       </c>
       <c r="AA105">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AB105">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="AC105">
-        <v>2.88</v>
+        <v>1.96</v>
       </c>
       <c r="AD105">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AG105">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK105">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18109,31 +18109,31 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z109">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG109">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK109">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>2.66</v>
       </c>
       <c r="Q110">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="R110">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S110">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T110">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U110">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V110">
         <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA110">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB110">
         <v>2</v>
       </c>
       <c r="AC110">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AD110">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF110">
         <v>1.58</v>
       </c>
       <c r="AG110">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AK110">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,34 +18402,34 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O111">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P111">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q111">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R111">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S111">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U111">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V111">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W111">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
         <v>1.01</v>
@@ -18441,25 +18441,25 @@
         <v>5</v>
       </c>
       <c r="AA111">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB111">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC111">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD111">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE111">
         <v>1.22</v>
       </c>
       <c r="AF111">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG111">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18577,13 +18577,13 @@
         <v>3.65</v>
       </c>
       <c r="R112">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S112">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U112">
         <v>2.25</v>
@@ -18592,37 +18592,37 @@
         <v>1.55</v>
       </c>
       <c r="W112">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z112">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA112">
         <v>1.57</v>
       </c>
       <c r="AB112">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC112">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD112">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE112">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF112">
         <v>1.5</v>
       </c>
       <c r="AG112">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AK112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,31 +18728,31 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O113">
-        <v>4.47</v>
+        <v>4.16</v>
       </c>
       <c r="P113">
-        <v>5.87</v>
+        <v>4.8</v>
       </c>
       <c r="Q113">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R113">
         <v>2.4</v>
       </c>
       <c r="S113">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U113">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V113">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W113">
         <v>1.13</v>
@@ -18761,47 +18761,47 @@
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z113">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA113">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB113">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AC113">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="AD113">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AE113">
+        <v>1.15</v>
+      </c>
+      <c r="AF113">
+        <v>1.67</v>
+      </c>
+      <c r="AG113">
+        <v>2.15</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
         <v>1.22</v>
       </c>
-      <c r="AF113">
-        <v>1.64</v>
-      </c>
-      <c r="AG113">
-        <v>2.12</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.1</v>
-      </c>
       <c r="AK113">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="O114">
         <v>4.3</v>
       </c>
       <c r="P114">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="Q114">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R114">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="S114">
         <v>1.25</v>
@@ -19054,58 +19054,58 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="O115">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P115">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
       </c>
       <c r="R115">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S115">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T115">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U115">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V115">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W115">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z115">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA115">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB115">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AC115">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD115">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE115">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF115">
         <v>1.58</v>
@@ -19127,7 +19127,7 @@
         <v>1.23</v>
       </c>
       <c r="AK115">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,7 +19220,7 @@
         <v>2</v>
       </c>
       <c r="O116">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P116">
         <v>3</v>
@@ -19229,31 +19229,31 @@
         <v>2.5</v>
       </c>
       <c r="R116">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S116">
         <v>1.2</v>
       </c>
       <c r="T116">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="U116">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="V116">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W116">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X116">
         <v>0</v>
       </c>
       <c r="Y116">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z116">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA116">
         <v>1.42</v>
@@ -19262,19 +19262,19 @@
         <v>2.8</v>
       </c>
       <c r="AC116">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AD116">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE116">
         <v>1.29</v>
       </c>
       <c r="AF116">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG116">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK116">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19395,13 +19395,13 @@
         <v>2.09</v>
       </c>
       <c r="S117">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T117">
+        <v>2.96</v>
+      </c>
+      <c r="U117">
         <v>2.7</v>
-      </c>
-      <c r="U117">
-        <v>2.89</v>
       </c>
       <c r="V117">
         <v>1.36</v>
@@ -19416,7 +19416,7 @@
         <v>1.25</v>
       </c>
       <c r="Z117">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA117">
         <v>1.9</v>
@@ -19437,7 +19437,7 @@
         <v>1.75</v>
       </c>
       <c r="AG117">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,61 +19543,61 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O118">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q118">
         <v>2.9</v>
       </c>
       <c r="R118">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S118">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T118">
         <v>2.75</v>
       </c>
       <c r="U118">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="V118">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z118">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA118">
         <v>1.83</v>
       </c>
       <c r="AB118">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AC118">
         <v>3.05</v>
       </c>
       <c r="AD118">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF118">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG118">
         <v>2.05</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK118">
         <v>1.42</v>
@@ -19748,7 +19748,7 @@
         <v>1.82</v>
       </c>
       <c r="AB119">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC119">
         <v>2.97</v>
@@ -19869,31 +19869,31 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="O120">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="P120">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q120">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R120">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S120">
         <v>1.2</v>
       </c>
       <c r="T120">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U120">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V120">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W120">
         <v>1.14</v>
@@ -19902,31 +19902,31 @@
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z120">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA120">
         <v>1.44</v>
       </c>
       <c r="AB120">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC120">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD120">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE120">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF120">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG120">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,58 +20032,58 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O121">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="P121">
         <v>9.5</v>
       </c>
       <c r="Q121">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R121">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S121">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T121">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="U121">
         <v>1.75</v>
       </c>
       <c r="V121">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W121">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X121">
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z121">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA121">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB121">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AC121">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AD121">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AE121">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AF121">
         <v>1.77</v>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK121">
         <v>4.5</v>
@@ -20195,16 +20195,16 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P122">
         <v>2.5</v>
       </c>
       <c r="Q122">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R122">
         <v>2.4</v>
@@ -20213,7 +20213,7 @@
         <v>1.22</v>
       </c>
       <c r="T122">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U122">
         <v>2.1</v>
@@ -20228,31 +20228,31 @@
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z122">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA122">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB122">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC122">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AD122">
         <v>1.73</v>
       </c>
       <c r="AE122">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF122">
         <v>1.4</v>
       </c>
       <c r="AG122">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
         <v>5.4</v>
       </c>
       <c r="R2">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
         <v>1.09</v>
@@ -671,28 +671,28 @@
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA2">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O3">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O4">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P4">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1133,25 +1133,25 @@
         <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R5">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S5">
         <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,13 +1160,13 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
         <v>2.62</v>
@@ -1175,13 +1175,13 @@
         <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
         <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
         <v>1.37</v>
@@ -1290,7 +1290,7 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="P6">
         <v>1.67</v>
@@ -1459,46 +1459,46 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R7">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="U7">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
+        <v>3.1</v>
+      </c>
+      <c r="AA7">
+        <v>1.9</v>
+      </c>
+      <c r="AB7">
+        <v>1.84</v>
+      </c>
+      <c r="AC7">
         <v>3.4</v>
       </c>
-      <c r="AA7">
-        <v>1.95</v>
-      </c>
-      <c r="AB7">
-        <v>1.85</v>
-      </c>
-      <c r="AC7">
-        <v>3.65</v>
-      </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1507,7 +1507,7 @@
         <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>3.39</v>
+        <v>3.62</v>
       </c>
       <c r="R8">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
         <v>1.01</v>
       </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>2.81</v>
+        <v>3.6</v>
       </c>
       <c r="AA8">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AC8">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O9">
+        <v>3.1</v>
+      </c>
+      <c r="P9">
+        <v>2.37</v>
+      </c>
+      <c r="Q9">
+        <v>3.39</v>
+      </c>
+      <c r="R9">
+        <v>1.94</v>
+      </c>
+      <c r="S9">
+        <v>1.49</v>
+      </c>
+      <c r="T9">
+        <v>2.55</v>
+      </c>
+      <c r="U9">
         <v>3.2</v>
       </c>
-      <c r="P9">
-        <v>2.3</v>
-      </c>
-      <c r="Q9">
-        <v>3.31</v>
-      </c>
-      <c r="R9">
-        <v>2.05</v>
-      </c>
-      <c r="S9">
-        <v>1.39</v>
-      </c>
-      <c r="T9">
-        <v>2.7</v>
-      </c>
-      <c r="U9">
-        <v>2.73</v>
-      </c>
       <c r="V9">
+        <v>1.28</v>
+      </c>
+      <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
         <v>1.4</v>
       </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.25</v>
-      </c>
       <c r="Z9">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AB9">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
         <v>2.32</v>
@@ -1960,19 +1960,19 @@
         <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1984,13 +1984,13 @@
         <v>2.63</v>
       </c>
       <c r="AC10">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AD10">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF10">
         <v>1.44</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="Q11">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
         <v>2.02</v>
@@ -2123,13 +2123,13 @@
         <v>2.62</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2141,25 +2141,25 @@
         <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="O12">
         <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
-        <v>2.95</v>
+        <v>3.36</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
         <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,13 +2434,13 @@
         <v>3.16</v>
       </c>
       <c r="P13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>3.56</v>
+        <v>4.21</v>
       </c>
       <c r="R13">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
         <v>1.39</v>
@@ -2452,7 +2452,7 @@
         <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.04</v>
@@ -2464,25 +2464,25 @@
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
         <v>1.82</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
         <v>2.1</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3569,55 +3569,55 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O20">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Q20">
         <v>2.7</v>
       </c>
       <c r="R20">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V20">
         <v>1.69</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>9.4</v>
+        <v>5.88</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC20">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD20">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AE20">
         <v>1.29</v>
@@ -3626,7 +3626,7 @@
         <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,43 +3741,43 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
         <v>5.48</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
         <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AD21">
         <v>1.45</v>
@@ -3786,10 +3786,10 @@
         <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,28 +3898,28 @@
         <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P22">
         <v>3.3</v>
       </c>
       <c r="Q22">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
         <v>2.08</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
         <v>2.81</v>
       </c>
       <c r="U22">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
         <v>1.04</v>
@@ -3931,19 +3931,19 @@
         <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="AA22">
         <v>1.96</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
         <v>1.11</v>
@@ -3952,7 +3952,7 @@
         <v>1.72</v>
       </c>
       <c r="AG22">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P26">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q26">
         <v>2.63</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
         <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
         <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB26">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="AC26">
         <v>2.42</v>
       </c>
       <c r="AD26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
@@ -4604,7 +4604,7 @@
         <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK26">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -4725,10 +4725,10 @@
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U27">
         <v>2.4</v>
@@ -4737,31 +4737,31 @@
         <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>4.19</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC27">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
         <v>1.66</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="O30">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q30">
-        <v>4.68</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA30">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD30">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AG30">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AK30">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P31">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>4.68</v>
       </c>
       <c r="R31">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U31">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
+        <v>1.11</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>3.75</v>
+      </c>
+      <c r="AA31">
+        <v>1.78</v>
+      </c>
+      <c r="AB31">
+        <v>1.93</v>
+      </c>
+      <c r="AC31">
+        <v>2.83</v>
+      </c>
+      <c r="AD31">
+        <v>1.37</v>
+      </c>
+      <c r="AE31">
         <v>1.13</v>
       </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
+      <c r="AF31">
+        <v>1.7</v>
+      </c>
+      <c r="AG31">
+        <v>2.03</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.87</v>
+      </c>
+      <c r="AK31">
         <v>1.14</v>
-      </c>
-      <c r="Z31">
-        <v>4.4</v>
-      </c>
-      <c r="AA31">
-        <v>1.57</v>
-      </c>
-      <c r="AB31">
-        <v>2.3</v>
-      </c>
-      <c r="AC31">
-        <v>2.35</v>
-      </c>
-      <c r="AD31">
-        <v>1.47</v>
-      </c>
-      <c r="AE31">
-        <v>1.16</v>
-      </c>
-      <c r="AF31">
-        <v>1.48</v>
-      </c>
-      <c r="AG31">
-        <v>2.45</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.55</v>
-      </c>
-      <c r="AK31">
-        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -5869,46 +5869,46 @@
         <v>1.32</v>
       </c>
       <c r="T34">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V34">
         <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB34">
         <v>2.07</v>
       </c>
       <c r="AC34">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
         <v>1.65</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
         <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="R44">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
         <v>2.94</v>
       </c>
       <c r="U44">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V44">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AA44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB44">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC44">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE44">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
         <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>1.89</v>
+      </c>
+      <c r="O48">
+        <v>3.75</v>
+      </c>
+      <c r="P48">
+        <v>3.3</v>
+      </c>
+      <c r="Q48">
+        <v>2.35</v>
+      </c>
+      <c r="R48">
         <v>2.3</v>
       </c>
-      <c r="O48">
-        <v>3.8</v>
-      </c>
-      <c r="P48">
+      <c r="S48">
+        <v>1.25</v>
+      </c>
+      <c r="T48">
+        <v>3.45</v>
+      </c>
+      <c r="U48">
+        <v>2.31</v>
+      </c>
+      <c r="V48">
+        <v>1.6</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.15</v>
+      </c>
+      <c r="Z48">
+        <v>4.3</v>
+      </c>
+      <c r="AA48">
+        <v>1.6</v>
+      </c>
+      <c r="AB48">
         <v>2.45</v>
       </c>
-      <c r="Q48">
-        <v>2.8</v>
-      </c>
-      <c r="R48">
-        <v>2.34</v>
-      </c>
-      <c r="S48">
-        <v>1.22</v>
-      </c>
-      <c r="T48">
-        <v>3.75</v>
-      </c>
-      <c r="U48">
-        <v>2.1</v>
-      </c>
-      <c r="V48">
-        <v>1.67</v>
-      </c>
-      <c r="W48">
-        <v>1.18</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.09</v>
-      </c>
-      <c r="Z48">
-        <v>5.35</v>
-      </c>
-      <c r="AA48">
+      <c r="AC48">
+        <v>2.38</v>
+      </c>
+      <c r="AD48">
         <v>1.47</v>
       </c>
-      <c r="AB48">
-        <v>2.88</v>
-      </c>
-      <c r="AC48">
-        <v>2.11</v>
-      </c>
-      <c r="AD48">
-        <v>1.7</v>
-      </c>
       <c r="AE48">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
+        <v>3.8</v>
+      </c>
+      <c r="P49">
+        <v>2.45</v>
+      </c>
+      <c r="Q49">
+        <v>2.8</v>
+      </c>
+      <c r="R49">
+        <v>2.34</v>
+      </c>
+      <c r="S49">
+        <v>1.22</v>
+      </c>
+      <c r="T49">
         <v>3.75</v>
       </c>
-      <c r="P49">
-        <v>3.3</v>
-      </c>
-      <c r="Q49">
-        <v>2.35</v>
-      </c>
-      <c r="R49">
-        <v>2.3</v>
-      </c>
-      <c r="S49">
-        <v>1.25</v>
-      </c>
-      <c r="T49">
-        <v>3.45</v>
-      </c>
       <c r="U49">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="V49">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z49">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA49">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB49">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AC49">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AD49">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AE49">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG49">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9627,7 +9627,7 @@
         <v>1.33</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
         <v>1</v>
@@ -9673,7 +9673,7 @@
         <v>1.67</v>
       </c>
       <c r="AK57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9778,10 +9778,10 @@
         <v>1.97</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T58">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U58">
         <v>3.08</v>
@@ -9947,10 +9947,10 @@
         <v>3</v>
       </c>
       <c r="U59">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V59">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
         <v>1.06</v>
@@ -9965,10 +9965,10 @@
         <v>3.28</v>
       </c>
       <c r="AA59">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB59">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC59">
         <v>3.2</v>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G60">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P66">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="Q66">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="R66">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="S66">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T66">
         <v>2.15</v>
       </c>
       <c r="U66">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V66">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W66">
         <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y66">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z66">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA66">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="AB66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC66">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="AD66">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE66">
         <v>1.02</v>
       </c>
       <c r="AF66">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="AG66">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>1.67</v>
+      </c>
+      <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
+        <v>5.5</v>
+      </c>
+      <c r="Q67">
+        <v>2.3</v>
+      </c>
+      <c r="R67">
         <v>1.91</v>
       </c>
-      <c r="O67">
-        <v>2.8</v>
-      </c>
-      <c r="P67">
-        <v>4.33</v>
-      </c>
-      <c r="Q67">
-        <v>2.71</v>
-      </c>
-      <c r="R67">
-        <v>1.74</v>
-      </c>
       <c r="S67">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T67">
         <v>2.15</v>
       </c>
       <c r="U67">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V67">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W67">
         <v>1.03</v>
       </c>
       <c r="X67">
+        <v>1.14</v>
+      </c>
+      <c r="Y67">
+        <v>1.65</v>
+      </c>
+      <c r="Z67">
+        <v>2.15</v>
+      </c>
+      <c r="AA67">
+        <v>3.07</v>
+      </c>
+      <c r="AB67">
+        <v>1.35</v>
+      </c>
+      <c r="AC67">
+        <v>6.41</v>
+      </c>
+      <c r="AD67">
         <v>1.1</v>
-      </c>
-      <c r="Y67">
-        <v>1.7</v>
-      </c>
-      <c r="Z67">
-        <v>2.06</v>
-      </c>
-      <c r="AA67">
-        <v>3.04</v>
-      </c>
-      <c r="AB67">
-        <v>1.33</v>
-      </c>
-      <c r="AC67">
-        <v>6.4</v>
-      </c>
-      <c r="AD67">
-        <v>1.05</v>
       </c>
       <c r="AE67">
         <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="AG67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12872,40 +12872,40 @@
         <v>1.88</v>
       </c>
       <c r="R77">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U77">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="V77">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="AA77">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB77">
         <v>2.08</v>
       </c>
       <c r="AC77">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD77">
         <v>1.37</v>
@@ -12914,10 +12914,10 @@
         <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG77">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK77">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13201,10 +13201,10 @@
         <v>1.83</v>
       </c>
       <c r="S79">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="T79">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="U79">
         <v>4</v>
@@ -13216,31 +13216,31 @@
         <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y79">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Z79">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AA79">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AB79">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC79">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="AD79">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE79">
         <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AG79">
         <v>1.44</v>
@@ -13259,7 +13259,7 @@
         <v>1.4</v>
       </c>
       <c r="AK79">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O85">
         <v>4.5</v>
@@ -14336,55 +14336,55 @@
         <v>3.98</v>
       </c>
       <c r="Q86">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R86">
         <v>2</v>
       </c>
       <c r="S86">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T86">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U86">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V86">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z86">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AA86">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB86">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC86">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AG86">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK86">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O88">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="P88">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R88">
         <v>2.3</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T88">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U88">
         <v>2.38</v>
@@ -14686,31 +14686,31 @@
         <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA88">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB88">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD88">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG88">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK88">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14991,7 +14991,7 @@
         <v>2.75</v>
       </c>
       <c r="R90">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S90">
         <v>1.62</v>
@@ -15009,7 +15009,7 @@
         <v>1.03</v>
       </c>
       <c r="X90">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y90">
         <v>1.66</v>
@@ -15018,7 +15018,7 @@
         <v>2.09</v>
       </c>
       <c r="AA90">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="AB90">
         <v>1.34</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O102">
         <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="Q102">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R102">
         <v>2.3</v>
       </c>
       <c r="S102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="U102">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="V102">
         <v>1.57</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z102">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB102">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC102">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD102">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AE102">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF102">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AG102">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="O103">
         <v>3.5</v>
       </c>
       <c r="P103">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="Q103">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T103">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U103">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V103">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA103">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AC103">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AD103">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK103">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="O104">
         <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2</v>
+        <v>3.57</v>
       </c>
       <c r="Q104">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="R104">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U104">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V104">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W104">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AA104">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB104">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC104">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD104">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AE104">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17596,40 +17596,40 @@
         <v>3.04</v>
       </c>
       <c r="Q106">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R106">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S106">
         <v>1.32</v>
       </c>
       <c r="T106">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U106">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W106">
         <v>1.08</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
         <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA106">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AB106">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC106">
         <v>2.88</v>
@@ -17641,10 +17641,10 @@
         <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK106">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,34 +17750,34 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="O107">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="P107">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q107">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S107">
         <v>1.28</v>
       </c>
       <c r="T107">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X107">
         <v>1.03</v>
@@ -17786,28 +17786,28 @@
         <v>1.14</v>
       </c>
       <c r="Z107">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB107">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC107">
         <v>2.53</v>
       </c>
       <c r="AD107">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE107">
         <v>1.14</v>
       </c>
       <c r="AF107">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK107">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL108">
         <v>0</v>

--- a/jogos_2026-07-25.xlsx
+++ b/jogos_2026-07-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>4.21</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.77</v>
+        <v>2.43</v>
       </c>
       <c r="O13">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q13">
-        <v>4.21</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
+        <v>1.3</v>
+      </c>
+      <c r="T20">
+        <v>3.3</v>
+      </c>
+      <c r="U20">
+        <v>2.4</v>
+      </c>
+      <c r="V20">
+        <v>1.45</v>
+      </c>
+      <c r="W20">
+        <v>1.12</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
         <v>1.2</v>
       </c>
-      <c r="T20">
-        <v>4</v>
-      </c>
-      <c r="U20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>1.69</v>
-      </c>
-      <c r="W20">
-        <v>1.16</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.12</v>
-      </c>
       <c r="Z20">
-        <v>5.88</v>
+        <v>5.48</v>
       </c>
       <c r="AA20">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="AD20">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="W21">
+        <v>1.16</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
         <v>1.12</v>
       </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
-      <c r="Y21">
-        <v>1.2</v>
-      </c>
       <c r="Z21">
-        <v>5.48</v>
+        <v>5.88</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r